--- a/Painel/faturamento.xlsx
+++ b/Painel/faturamento.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp_811_10-2022\htdocs\FNDE\Painel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp_82\htdocs\FNDE\Painel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17290,7 +17290,7 @@
         <v>48</v>
       </c>
       <c r="P2" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q2" s="2">
         <v>30599.999999999996</v>
@@ -17352,7 +17352,7 @@
         <v>34</v>
       </c>
       <c r="P3" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q3" s="2">
         <v>21675</v>
@@ -17414,7 +17414,7 @@
         <v>34</v>
       </c>
       <c r="P4" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q4" s="2">
         <v>21675</v>
@@ -17476,7 +17476,7 @@
         <v>64</v>
       </c>
       <c r="P5" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q5" s="2">
         <v>40800</v>
@@ -17538,7 +17538,7 @@
         <v>34</v>
       </c>
       <c r="P6" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q6" s="2">
         <v>21675</v>
@@ -17600,7 +17600,7 @@
         <v>33</v>
       </c>
       <c r="P7" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q7" s="2">
         <v>21037.5</v>
@@ -17662,7 +17662,7 @@
         <v>34</v>
       </c>
       <c r="P8" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q8" s="2">
         <v>21675</v>
@@ -17724,7 +17724,7 @@
         <v>44</v>
       </c>
       <c r="P9" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q9" s="2">
         <v>28049.999999999996</v>
@@ -17786,7 +17786,7 @@
         <v>34</v>
       </c>
       <c r="P10" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q10" s="2">
         <v>21675</v>
@@ -17848,7 +17848,7 @@
         <v>33</v>
       </c>
       <c r="P11" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q11" s="2">
         <v>21037.5</v>
@@ -17910,7 +17910,7 @@
         <v>34</v>
       </c>
       <c r="P12" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q12" s="2">
         <v>21675</v>
@@ -17972,7 +17972,7 @@
         <v>24</v>
       </c>
       <c r="P13" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q13" s="2">
         <v>15299.999999999998</v>
@@ -18034,7 +18034,7 @@
         <v>42</v>
       </c>
       <c r="P14" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q14" s="2">
         <v>26774.999999999996</v>
@@ -18096,7 +18096,7 @@
         <v>24</v>
       </c>
       <c r="P15" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q15" s="2">
         <v>15299.999999999998</v>
@@ -18158,7 +18158,7 @@
         <v>36</v>
       </c>
       <c r="P16" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q16" s="2">
         <v>22950</v>
@@ -18220,7 +18220,7 @@
         <v>34</v>
       </c>
       <c r="P17" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q17" s="2">
         <v>21501.599999999999</v>
@@ -18282,7 +18282,7 @@
         <v>24</v>
       </c>
       <c r="P18" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q18" s="2">
         <v>15177.599999999999</v>
@@ -18344,7 +18344,7 @@
         <v>33</v>
       </c>
       <c r="P19" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q19" s="2">
         <v>20869.199999999997</v>
@@ -18406,7 +18406,7 @@
         <v>40</v>
       </c>
       <c r="P20" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q20" s="2">
         <v>25296</v>
@@ -18468,7 +18468,7 @@
         <v>25</v>
       </c>
       <c r="P21" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q21" s="2">
         <v>15809.999999999998</v>
@@ -18530,7 +18530,7 @@
         <v>49</v>
       </c>
       <c r="P22" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q22" s="2">
         <v>30987.599999999999</v>
@@ -18592,7 +18592,7 @@
         <v>37</v>
       </c>
       <c r="P23" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q23" s="2">
         <v>23398.799999999999</v>
@@ -18654,7 +18654,7 @@
         <v>38</v>
       </c>
       <c r="P24" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q24" s="2">
         <v>23934.3</v>
@@ -18716,7 +18716,7 @@
         <v>38</v>
       </c>
       <c r="P25" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q25" s="2">
         <v>23934.3</v>
@@ -18778,7 +18778,7 @@
         <v>24</v>
       </c>
       <c r="P26" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q26" s="2">
         <v>15116.4</v>
@@ -18840,7 +18840,7 @@
         <v>27</v>
       </c>
       <c r="P27" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q27" s="2">
         <v>17005.949999999997</v>
@@ -18902,7 +18902,7 @@
         <v>44</v>
       </c>
       <c r="P28" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q28" s="2">
         <v>27713.399999999998</v>
@@ -18964,7 +18964,7 @@
         <v>35</v>
       </c>
       <c r="P29" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q29" s="2">
         <v>22044.75</v>
@@ -19026,7 +19026,7 @@
         <v>24</v>
       </c>
       <c r="P30" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q30" s="2">
         <v>15116.4</v>
@@ -19088,7 +19088,7 @@
         <v>24</v>
       </c>
       <c r="P31" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q31" s="2">
         <v>15116.4</v>
@@ -19150,7 +19150,7 @@
         <v>27</v>
       </c>
       <c r="P32" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q32" s="2">
         <v>17005.949999999997</v>
@@ -19212,7 +19212,7 @@
         <v>40</v>
       </c>
       <c r="P33" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q33" s="2">
         <v>25194</v>
@@ -19274,7 +19274,7 @@
         <v>47</v>
       </c>
       <c r="P34" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q34" s="2">
         <v>29602.949999999997</v>
@@ -19336,7 +19336,7 @@
         <v>47</v>
       </c>
       <c r="P35" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q35" s="2">
         <v>29602.949999999997</v>
@@ -19398,7 +19398,7 @@
         <v>44</v>
       </c>
       <c r="P36" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q36" s="2">
         <v>27713.399999999998</v>
@@ -19460,7 +19460,7 @@
         <v>41</v>
       </c>
       <c r="P37" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q37" s="2">
         <v>25823.85</v>
@@ -19522,7 +19522,7 @@
         <v>25</v>
       </c>
       <c r="P38" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q38" s="2">
         <v>15746.249999999998</v>
@@ -19584,7 +19584,7 @@
         <v>39</v>
       </c>
       <c r="P39" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q39" s="2">
         <v>24265.8</v>
@@ -19646,7 +19646,7 @@
         <v>35</v>
       </c>
       <c r="P40" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q40" s="2">
         <v>21777</v>
@@ -19708,7 +19708,7 @@
         <v>39</v>
       </c>
       <c r="P41" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q41" s="2">
         <v>24265.8</v>
@@ -19770,7 +19770,7 @@
         <v>31</v>
       </c>
       <c r="P42" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q42" s="2">
         <v>19288.199999999997</v>
@@ -19832,7 +19832,7 @@
         <v>36</v>
       </c>
       <c r="P43" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q43" s="2">
         <v>22399.199999999997</v>
@@ -19894,7 +19894,7 @@
         <v>41</v>
       </c>
       <c r="P44" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q44" s="2">
         <v>25510.199999999997</v>
@@ -19956,7 +19956,7 @@
         <v>34</v>
       </c>
       <c r="P45" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q45" s="2">
         <v>21154.799999999999</v>
@@ -20018,7 +20018,7 @@
         <v>24</v>
       </c>
       <c r="P46" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q46" s="2">
         <v>14932.8</v>
@@ -20080,7 +20080,7 @@
         <v>49</v>
       </c>
       <c r="P47" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q47" s="2">
         <v>30487.8</v>
@@ -20142,7 +20142,7 @@
         <v>39</v>
       </c>
       <c r="P48" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q48" s="2">
         <v>24265.8</v>
@@ -20204,7 +20204,7 @@
         <v>25</v>
       </c>
       <c r="P49" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q49" s="2">
         <v>15554.999999999998</v>
@@ -20266,7 +20266,7 @@
         <v>39</v>
       </c>
       <c r="P50" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q50" s="2">
         <v>24265.8</v>
@@ -20328,7 +20328,7 @@
         <v>37</v>
       </c>
       <c r="P51" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q51" s="2">
         <v>23021.399999999998</v>
@@ -20390,7 +20390,7 @@
         <v>24</v>
       </c>
       <c r="P52" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q52" s="2">
         <v>14871.599999999999</v>
@@ -20452,7 +20452,7 @@
         <v>33</v>
       </c>
       <c r="P53" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q53" s="2">
         <v>20448.449999999997</v>
@@ -20514,7 +20514,7 @@
         <v>36</v>
       </c>
       <c r="P54" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q54" s="2">
         <v>22307.399999999998</v>
@@ -20576,7 +20576,7 @@
         <v>24</v>
       </c>
       <c r="P55" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q55" s="2">
         <v>14871.599999999999</v>
@@ -20638,7 +20638,7 @@
         <v>46</v>
       </c>
       <c r="P56" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q56" s="2">
         <v>28503.899999999998</v>
@@ -20700,7 +20700,7 @@
         <v>31</v>
       </c>
       <c r="P57" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q57" s="2">
         <v>19209.149999999998</v>
@@ -20762,7 +20762,7 @@
         <v>38</v>
       </c>
       <c r="P58" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q58" s="2">
         <v>23546.699999999997</v>
@@ -20824,7 +20824,7 @@
         <v>24</v>
       </c>
       <c r="P59" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q59" s="2">
         <v>14871.599999999999</v>
@@ -20886,7 +20886,7 @@
         <v>33</v>
       </c>
       <c r="P60" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q60" s="2">
         <v>20448.449999999997</v>
@@ -20948,7 +20948,7 @@
         <v>34</v>
       </c>
       <c r="P61" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q61" s="2">
         <v>21068.1</v>
@@ -21010,7 +21010,7 @@
         <v>28</v>
       </c>
       <c r="P62" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q62" s="2">
         <v>17350.199999999997</v>
@@ -21072,7 +21072,7 @@
         <v>37</v>
       </c>
       <c r="P63" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q63" s="2">
         <v>22927.05</v>
@@ -21134,7 +21134,7 @@
         <v>34</v>
       </c>
       <c r="P64" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q64" s="2">
         <v>21068.1</v>
@@ -21196,7 +21196,7 @@
         <v>31</v>
       </c>
       <c r="P65" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q65" s="2">
         <v>19209.149999999998</v>
@@ -21258,7 +21258,7 @@
         <v>59</v>
       </c>
       <c r="P66" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q66" s="2">
         <v>36559.35</v>
@@ -21320,7 +21320,7 @@
         <v>38</v>
       </c>
       <c r="P67" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q67" s="2">
         <v>23546.699999999997</v>
@@ -21382,7 +21382,7 @@
         <v>31</v>
       </c>
       <c r="P68" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q68" s="2">
         <v>19209.149999999998</v>
@@ -21444,7 +21444,7 @@
         <v>38</v>
       </c>
       <c r="P69" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q69" s="2">
         <v>23546.699999999997</v>
@@ -21506,7 +21506,7 @@
         <v>32</v>
       </c>
       <c r="P70" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q70" s="2">
         <v>19828.8</v>
@@ -21568,7 +21568,7 @@
         <v>37</v>
       </c>
       <c r="P71" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q71" s="2">
         <v>22927.05</v>
@@ -21630,7 +21630,7 @@
         <v>25</v>
       </c>
       <c r="P72" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q72" s="2">
         <v>15491.249999999998</v>
@@ -21692,7 +21692,7 @@
         <v>25</v>
       </c>
       <c r="P73" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q73" s="2">
         <v>15491.249999999998</v>
@@ -21754,7 +21754,7 @@
         <v>53</v>
       </c>
       <c r="P74" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q74" s="2">
         <v>32841.449999999997</v>
@@ -21816,7 +21816,7 @@
         <v>34</v>
       </c>
       <c r="P75" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q75" s="2">
         <v>21068.1</v>
@@ -21878,7 +21878,7 @@
         <v>46</v>
       </c>
       <c r="P76" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q76" s="2">
         <v>28503.899999999998</v>
@@ -21940,7 +21940,7 @@
         <v>34</v>
       </c>
       <c r="P77" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q77" s="2">
         <v>21068.1</v>
@@ -22002,7 +22002,7 @@
         <v>47</v>
       </c>
       <c r="P78" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q78" s="2">
         <v>29123.55</v>
@@ -22064,7 +22064,7 @@
         <v>32</v>
       </c>
       <c r="P79" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q79" s="2">
         <v>19828.8</v>
@@ -22126,7 +22126,7 @@
         <v>132</v>
       </c>
       <c r="P80" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q80" s="2">
         <v>81120.599999999991</v>
@@ -22188,7 +22188,7 @@
         <v>35</v>
       </c>
       <c r="P81" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q81" s="2">
         <v>21509.25</v>
@@ -22250,7 +22250,7 @@
         <v>34</v>
       </c>
       <c r="P82" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q82" s="2">
         <v>20894.699999999997</v>
@@ -22312,7 +22312,7 @@
         <v>64</v>
       </c>
       <c r="P83" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q83" s="2">
         <v>39331.199999999997</v>
@@ -22374,7 +22374,7 @@
         <v>31</v>
       </c>
       <c r="P84" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q84" s="2">
         <v>19051.05</v>
@@ -22436,7 +22436,7 @@
         <v>43</v>
       </c>
       <c r="P85" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q85" s="2">
         <v>26425.649999999998</v>
@@ -22498,7 +22498,7 @@
         <v>38</v>
       </c>
       <c r="P86" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q86" s="2">
         <v>23352.899999999998</v>
@@ -22560,7 +22560,7 @@
         <v>45</v>
       </c>
       <c r="P87" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q87" s="2">
         <v>27654.749999999996</v>
@@ -22622,7 +22622,7 @@
         <v>40</v>
       </c>
       <c r="P88" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q88" s="2">
         <v>24582</v>
@@ -22684,7 +22684,7 @@
         <v>34</v>
       </c>
       <c r="P89" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q89" s="2">
         <v>20894.699999999997</v>
@@ -22746,7 +22746,7 @@
         <v>44</v>
       </c>
       <c r="P90" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q90" s="2">
         <v>27040.199999999997</v>
@@ -22808,7 +22808,7 @@
         <v>34</v>
       </c>
       <c r="P91" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q91" s="2">
         <v>20894.699999999997</v>
@@ -22870,7 +22870,7 @@
         <v>36</v>
       </c>
       <c r="P92" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q92" s="2">
         <v>22123.8</v>
@@ -22932,7 +22932,7 @@
         <v>42</v>
       </c>
       <c r="P93" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q93" s="2">
         <v>25811.1</v>
@@ -22994,7 +22994,7 @@
         <v>42</v>
       </c>
       <c r="P94" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q94" s="2">
         <v>25811.1</v>
@@ -23056,7 +23056,7 @@
         <v>38</v>
       </c>
       <c r="P95" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q95" s="2">
         <v>23352.899999999998</v>
@@ -23118,7 +23118,7 @@
         <v>34</v>
       </c>
       <c r="P96" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q96" s="2">
         <v>20894.699999999997</v>
@@ -23180,7 +23180,7 @@
         <v>37</v>
       </c>
       <c r="P97" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q97" s="2">
         <v>22738.35</v>
@@ -23242,7 +23242,7 @@
         <v>29</v>
       </c>
       <c r="P98" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q98" s="2">
         <v>17821.949999999997</v>
@@ -23304,7 +23304,7 @@
         <v>34</v>
       </c>
       <c r="P99" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q99" s="2">
         <v>20894.699999999997</v>
@@ -23366,7 +23366,7 @@
         <v>35</v>
       </c>
       <c r="P100" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q100" s="2">
         <v>21509.25</v>
@@ -23428,7 +23428,7 @@
         <v>62</v>
       </c>
       <c r="P101" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q101" s="2">
         <v>38102.1</v>
@@ -23490,7 +23490,7 @@
         <v>29</v>
       </c>
       <c r="P102" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q102" s="2">
         <v>17821.949999999997</v>
@@ -23552,7 +23552,7 @@
         <v>33</v>
       </c>
       <c r="P103" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q103" s="2">
         <v>20196</v>
@@ -23614,7 +23614,7 @@
         <v>47</v>
       </c>
       <c r="P104" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q104" s="2">
         <v>28763.999999999996</v>
@@ -23676,7 +23676,7 @@
         <v>51</v>
       </c>
       <c r="P105" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q105" s="2">
         <v>31211.999999999996</v>
@@ -23738,7 +23738,7 @@
         <v>31</v>
       </c>
       <c r="P106" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q106" s="2">
         <v>18972</v>
@@ -23800,7 +23800,7 @@
         <v>46</v>
       </c>
       <c r="P107" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q107" s="2">
         <v>28151.999999999996</v>
@@ -23862,7 +23862,7 @@
         <v>37</v>
       </c>
       <c r="P108" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q108" s="2">
         <v>22644</v>
@@ -23924,7 +23924,7 @@
         <v>46</v>
       </c>
       <c r="P109" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q109" s="2">
         <v>28151.999999999996</v>
@@ -23986,7 +23986,7 @@
         <v>41</v>
       </c>
       <c r="P110" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q110" s="2">
         <v>25092</v>
@@ -24048,7 +24048,7 @@
         <v>34</v>
       </c>
       <c r="P111" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q111" s="2">
         <v>20808</v>
@@ -24110,7 +24110,7 @@
         <v>24</v>
       </c>
       <c r="P112" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q112" s="2">
         <v>14687.999999999998</v>
@@ -24172,7 +24172,7 @@
         <v>36</v>
       </c>
       <c r="P113" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q113" s="2">
         <v>22032</v>
@@ -24234,7 +24234,7 @@
         <v>46</v>
       </c>
       <c r="P114" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q114" s="2">
         <v>28151.999999999996</v>
@@ -24296,7 +24296,7 @@
         <v>32</v>
       </c>
       <c r="P115" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q115" s="2">
         <v>19584</v>
@@ -24358,7 +24358,7 @@
         <v>24</v>
       </c>
       <c r="P116" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q116" s="2">
         <v>14687.999999999998</v>
@@ -24420,7 +24420,7 @@
         <v>33</v>
       </c>
       <c r="P117" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q117" s="2">
         <v>20196</v>
@@ -24482,7 +24482,7 @@
         <v>29</v>
       </c>
       <c r="P118" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q118" s="2">
         <v>17748</v>
@@ -24544,7 +24544,7 @@
         <v>29</v>
       </c>
       <c r="P119" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q119" s="2">
         <v>17748</v>
@@ -24606,7 +24606,7 @@
         <v>36</v>
       </c>
       <c r="P120" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q120" s="2">
         <v>22032</v>
@@ -24668,7 +24668,7 @@
         <v>41</v>
       </c>
       <c r="P121" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q121" s="2">
         <v>25092</v>
@@ -24730,7 +24730,7 @@
         <v>39</v>
       </c>
       <c r="P122" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q122" s="2">
         <v>23868</v>
@@ -24792,7 +24792,7 @@
         <v>40</v>
       </c>
       <c r="P123" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q123" s="2">
         <v>24480</v>
@@ -24854,7 +24854,7 @@
         <v>24</v>
       </c>
       <c r="P124" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q124" s="2">
         <v>14687.999999999998</v>
@@ -24916,7 +24916,7 @@
         <v>121</v>
       </c>
       <c r="P125" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q125" s="2">
         <v>74052</v>
@@ -24978,7 +24978,7 @@
         <v>29</v>
       </c>
       <c r="P126" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q126" s="2">
         <v>17748</v>
@@ -25040,7 +25040,7 @@
         <v>55</v>
       </c>
       <c r="P127" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q127" s="2">
         <v>33660</v>
@@ -25102,7 +25102,7 @@
         <v>26</v>
       </c>
       <c r="P128" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q128" s="2">
         <v>15911.999999999998</v>
@@ -25164,7 +25164,7 @@
         <v>37</v>
       </c>
       <c r="P129" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q129" s="2">
         <v>22644</v>
@@ -25226,7 +25226,7 @@
         <v>27</v>
       </c>
       <c r="P130" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q130" s="2">
         <v>16524</v>
@@ -25288,7 +25288,7 @@
         <v>47</v>
       </c>
       <c r="P131" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q131" s="2">
         <v>28763.999999999996</v>
@@ -25350,7 +25350,7 @@
         <v>33</v>
       </c>
       <c r="P132" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q132" s="2">
         <v>20196</v>
@@ -25412,7 +25412,7 @@
         <v>37</v>
       </c>
       <c r="P133" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q133" s="2">
         <v>22644</v>
@@ -25474,7 +25474,7 @@
         <v>32</v>
       </c>
       <c r="P134" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q134" s="2">
         <v>19584</v>
@@ -25536,7 +25536,7 @@
         <v>34</v>
       </c>
       <c r="P135" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q135" s="2">
         <v>20808</v>
@@ -25598,7 +25598,7 @@
         <v>29</v>
       </c>
       <c r="P136" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q136" s="2">
         <v>17748</v>
@@ -25660,7 +25660,7 @@
         <v>25</v>
       </c>
       <c r="P137" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q137" s="2">
         <v>15299.999999999998</v>
@@ -25722,7 +25722,7 @@
         <v>42</v>
       </c>
       <c r="P138" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q138" s="2">
         <v>25382.699999999997</v>
@@ -25784,7 +25784,7 @@
         <v>49</v>
       </c>
       <c r="P139" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q139" s="2">
         <v>29613.149999999998</v>
@@ -25846,7 +25846,7 @@
         <v>36</v>
       </c>
       <c r="P140" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q140" s="2">
         <v>21756.6</v>
@@ -25908,7 +25908,7 @@
         <v>34</v>
       </c>
       <c r="P141" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q141" s="2">
         <v>20547.899999999998</v>
@@ -25970,7 +25970,7 @@
         <v>34</v>
       </c>
       <c r="P142" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q142" s="2">
         <v>20547.899999999998</v>
@@ -26032,7 +26032,7 @@
         <v>33</v>
       </c>
       <c r="P143" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q143" s="2">
         <v>19943.55</v>
@@ -26094,7 +26094,7 @@
         <v>34</v>
       </c>
       <c r="P144" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q144" s="2">
         <v>20547.899999999998</v>
@@ -26156,7 +26156,7 @@
         <v>27</v>
       </c>
       <c r="P145" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q145" s="2">
         <v>16317.449999999999</v>
@@ -26218,7 +26218,7 @@
         <v>29</v>
       </c>
       <c r="P146" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q146" s="2">
         <v>17526.149999999998</v>
@@ -26280,7 +26280,7 @@
         <v>36</v>
       </c>
       <c r="P147" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q147" s="2">
         <v>21756.6</v>
@@ -26342,7 +26342,7 @@
         <v>24</v>
       </c>
       <c r="P148" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q148" s="2">
         <v>14504.4</v>
@@ -26404,7 +26404,7 @@
         <v>34</v>
       </c>
       <c r="P149" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q149" s="2">
         <v>20547.899999999998</v>
@@ -26466,7 +26466,7 @@
         <v>32</v>
       </c>
       <c r="P150" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q150" s="2">
         <v>19339.199999999997</v>
@@ -26528,7 +26528,7 @@
         <v>56</v>
       </c>
       <c r="P151" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q151" s="2">
         <v>33843.599999999999</v>
@@ -26590,7 +26590,7 @@
         <v>25</v>
       </c>
       <c r="P152" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q152" s="2">
         <v>15108.749999999998</v>
@@ -26652,7 +26652,7 @@
         <v>47</v>
       </c>
       <c r="P153" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q153" s="2">
         <v>28404.449999999997</v>
@@ -26714,7 +26714,7 @@
         <v>25</v>
       </c>
       <c r="P154" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q154" s="2">
         <v>15108.749999999998</v>
@@ -26776,7 +26776,7 @@
         <v>51</v>
       </c>
       <c r="P155" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q155" s="2">
         <v>30821.85</v>
@@ -26838,7 +26838,7 @@
         <v>25</v>
       </c>
       <c r="P156" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q156" s="2">
         <v>15108.749999999998</v>
@@ -26900,7 +26900,7 @@
         <v>24</v>
       </c>
       <c r="P157" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q157" s="2">
         <v>14504.4</v>
@@ -26962,7 +26962,7 @@
         <v>25</v>
       </c>
       <c r="P158" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q158" s="2">
         <v>15108.749999999998</v>
@@ -27024,7 +27024,7 @@
         <v>24</v>
       </c>
       <c r="P159" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q159" s="2">
         <v>14504.4</v>
@@ -27086,7 +27086,7 @@
         <v>51</v>
       </c>
       <c r="P160" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q160" s="2">
         <v>30821.85</v>
@@ -27148,7 +27148,7 @@
         <v>28</v>
       </c>
       <c r="P161" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q161" s="2">
         <v>16921.8</v>
@@ -27210,7 +27210,7 @@
         <v>44</v>
       </c>
       <c r="P162" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q162" s="2">
         <v>26591.399999999998</v>
@@ -27272,7 +27272,7 @@
         <v>40</v>
       </c>
       <c r="P163" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q163" s="2">
         <v>24174</v>
@@ -27334,7 +27334,7 @@
         <v>94</v>
       </c>
       <c r="P164" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q164" s="2">
         <v>56808.899999999994</v>
@@ -27396,7 +27396,7 @@
         <v>67</v>
       </c>
       <c r="P165" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q165" s="2">
         <v>40491.449999999997</v>
@@ -27458,7 +27458,7 @@
         <v>34</v>
       </c>
       <c r="P166" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q166" s="2">
         <v>20287.8</v>
@@ -27520,7 +27520,7 @@
         <v>36</v>
       </c>
       <c r="P167" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q167" s="2">
         <v>21481.199999999997</v>
@@ -27582,7 +27582,7 @@
         <v>30</v>
       </c>
       <c r="P168" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q168" s="2">
         <v>17901</v>
@@ -27644,7 +27644,7 @@
         <v>53</v>
       </c>
       <c r="P169" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q169" s="2">
         <v>31625.1</v>
@@ -27706,7 +27706,7 @@
         <v>26</v>
       </c>
       <c r="P170" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q170" s="2">
         <v>15514.199999999999</v>
@@ -27768,7 +27768,7 @@
         <v>32</v>
       </c>
       <c r="P171" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q171" s="2">
         <v>19094.399999999998</v>
@@ -27830,7 +27830,7 @@
         <v>24</v>
       </c>
       <c r="P172" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q172" s="2">
         <v>14320.8</v>
@@ -27892,7 +27892,7 @@
         <v>34</v>
       </c>
       <c r="P173" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q173" s="2">
         <v>20287.8</v>
@@ -27954,7 +27954,7 @@
         <v>33</v>
       </c>
       <c r="P174" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q174" s="2">
         <v>19691.099999999999</v>
@@ -28016,7 +28016,7 @@
         <v>55</v>
       </c>
       <c r="P175" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q175" s="2">
         <v>32818.5</v>
@@ -28078,7 +28078,7 @@
         <v>45</v>
       </c>
       <c r="P176" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q176" s="2">
         <v>26851.499999999996</v>
@@ -28140,7 +28140,7 @@
         <v>36</v>
       </c>
       <c r="P177" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q177" s="2">
         <v>21481.199999999997</v>
@@ -28202,7 +28202,7 @@
         <v>64</v>
       </c>
       <c r="P178" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q178" s="2">
         <v>38188.799999999996</v>
@@ -28264,7 +28264,7 @@
         <v>51</v>
       </c>
       <c r="P179" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q179" s="2">
         <v>30431.699999999997</v>
@@ -28326,7 +28326,7 @@
         <v>35</v>
       </c>
       <c r="P180" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q180" s="2">
         <v>20884.5</v>
@@ -28388,7 +28388,7 @@
         <v>35</v>
       </c>
       <c r="P181" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q181" s="2">
         <v>20884.5</v>
@@ -28450,7 +28450,7 @@
         <v>51</v>
       </c>
       <c r="P182" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q182" s="2">
         <v>30431.699999999997</v>
@@ -28512,7 +28512,7 @@
         <v>48</v>
       </c>
       <c r="P183" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q183" s="2">
         <v>28641.599999999999</v>
@@ -28574,7 +28574,7 @@
         <v>39</v>
       </c>
       <c r="P184" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q184" s="2">
         <v>25658.1</v>
@@ -28636,7 +28636,7 @@
         <v>24</v>
       </c>
       <c r="P185" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q185" s="2">
         <v>15789.599999999999</v>
@@ -28698,7 +28698,7 @@
         <v>39</v>
       </c>
       <c r="P186" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q186" s="2">
         <v>25658.1</v>
@@ -28760,7 +28760,7 @@
         <v>24</v>
       </c>
       <c r="P187" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q187" s="2">
         <v>15789.599999999999</v>
@@ -28822,7 +28822,7 @@
         <v>39</v>
       </c>
       <c r="P188" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q188" s="2">
         <v>25658.1</v>
@@ -28884,7 +28884,7 @@
         <v>28</v>
       </c>
       <c r="P189" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q189" s="2">
         <v>18421.199999999997</v>
@@ -28946,7 +28946,7 @@
         <v>64</v>
       </c>
       <c r="P190" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q190" s="2">
         <v>42105.599999999999</v>
@@ -29008,7 +29008,7 @@
         <v>34</v>
       </c>
       <c r="P191" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q191" s="2">
         <v>22368.6</v>
@@ -29070,7 +29070,7 @@
         <v>27</v>
       </c>
       <c r="P192" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q192" s="2">
         <v>17763.3</v>
@@ -29132,7 +29132,7 @@
         <v>64</v>
       </c>
       <c r="P193" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q193" s="2">
         <v>42105.599999999999</v>
@@ -29194,7 +29194,7 @@
         <v>104</v>
       </c>
       <c r="P194" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q194" s="2">
         <v>68421.599999999991</v>
@@ -29256,7 +29256,7 @@
         <v>38</v>
       </c>
       <c r="P195" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q195" s="2">
         <v>24903.3</v>
@@ -29318,7 +29318,7 @@
         <v>33</v>
       </c>
       <c r="P196" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q196" s="2">
         <v>21626.55</v>
@@ -29380,7 +29380,7 @@
         <v>34</v>
       </c>
       <c r="P197" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q197" s="2">
         <v>22281.899999999998</v>
@@ -29442,7 +29442,7 @@
         <v>103</v>
       </c>
       <c r="P198" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q198" s="2">
         <v>67501.049999999988</v>
@@ -29504,7 +29504,7 @@
         <v>32</v>
       </c>
       <c r="P199" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q199" s="2">
         <v>20971.199999999997</v>
@@ -29566,7 +29566,7 @@
         <v>45</v>
       </c>
       <c r="P200" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q200" s="2">
         <v>29490.749999999996</v>
@@ -29628,7 +29628,7 @@
         <v>47</v>
       </c>
       <c r="P201" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q201" s="2">
         <v>30801.449999999997</v>
@@ -29690,7 +29690,7 @@
         <v>30</v>
       </c>
       <c r="P202" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q202" s="2">
         <v>19660.5</v>
@@ -29752,7 +29752,7 @@
         <v>49</v>
       </c>
       <c r="P203" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q203" s="2">
         <v>32112.149999999998</v>
@@ -29814,7 +29814,7 @@
         <v>25</v>
       </c>
       <c r="P204" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q204" s="2">
         <v>16383.749999999998</v>
@@ -29876,7 +29876,7 @@
         <v>38</v>
       </c>
       <c r="P205" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q205" s="2">
         <v>24903.3</v>
@@ -29938,7 +29938,7 @@
         <v>28</v>
       </c>
       <c r="P206" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q206" s="2">
         <v>18349.8</v>
@@ -30000,7 +30000,7 @@
         <v>87</v>
       </c>
       <c r="P207" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q207" s="2">
         <v>57015.45</v>
@@ -30062,7 +30062,7 @@
         <v>38</v>
       </c>
       <c r="P208" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q208" s="2">
         <v>24903.3</v>
@@ -30124,7 +30124,7 @@
         <v>25</v>
       </c>
       <c r="P209" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q209" s="2">
         <v>14981.249999999998</v>
@@ -30186,7 +30186,7 @@
         <v>45</v>
       </c>
       <c r="P210" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q210" s="2">
         <v>26966.249999999996</v>
@@ -30248,7 +30248,7 @@
         <v>26</v>
       </c>
       <c r="P211" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q211" s="2">
         <v>15580.499999999998</v>
@@ -30310,7 +30310,7 @@
         <v>65</v>
       </c>
       <c r="P212" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q212" s="2">
         <v>38951.25</v>
@@ -30372,7 +30372,7 @@
         <v>31</v>
       </c>
       <c r="P213" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q213" s="2">
         <v>18576.75</v>
@@ -30434,7 +30434,7 @@
         <v>42</v>
       </c>
       <c r="P214" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q214" s="2">
         <v>25168.5</v>
@@ -30496,7 +30496,7 @@
         <v>76</v>
       </c>
       <c r="P215" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q215" s="2">
         <v>45543</v>
@@ -30558,7 +30558,7 @@
         <v>24</v>
       </c>
       <c r="P216" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q216" s="2">
         <v>14381.999999999998</v>
@@ -30620,7 +30620,7 @@
         <v>29</v>
       </c>
       <c r="P217" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q217" s="2">
         <v>17378.25</v>
@@ -30682,7 +30682,7 @@
         <v>36</v>
       </c>
       <c r="P218" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q218" s="2">
         <v>21573</v>
@@ -30744,7 +30744,7 @@
         <v>33</v>
       </c>
       <c r="P219" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q219" s="2">
         <v>19775.25</v>
@@ -30806,7 +30806,7 @@
         <v>25</v>
       </c>
       <c r="P220" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q220" s="2">
         <v>14981.249999999998</v>
@@ -30868,7 +30868,7 @@
         <v>37</v>
       </c>
       <c r="P221" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q221" s="2">
         <v>22172.25</v>
@@ -30930,7 +30930,7 @@
         <v>53</v>
       </c>
       <c r="P222" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q222" s="2">
         <v>31760.249999999996</v>
@@ -30992,7 +30992,7 @@
         <v>27</v>
       </c>
       <c r="P223" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q223" s="2">
         <v>16179.749999999998</v>
@@ -31054,7 +31054,7 @@
         <v>46</v>
       </c>
       <c r="P224" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q224" s="2">
         <v>27565.499999999996</v>
@@ -31116,7 +31116,7 @@
         <v>44</v>
       </c>
       <c r="P225" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q225" s="2">
         <v>26366.999999999996</v>
@@ -31178,7 +31178,7 @@
         <v>49</v>
       </c>
       <c r="P226" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q226" s="2">
         <v>29363.249999999996</v>
@@ -31240,7 +31240,7 @@
         <v>34</v>
       </c>
       <c r="P227" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q227" s="2">
         <v>20374.5</v>
@@ -31302,7 +31302,7 @@
         <v>25</v>
       </c>
       <c r="P228" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q228" s="2">
         <v>14981.249999999998</v>
@@ -31364,7 +31364,7 @@
         <v>34</v>
       </c>
       <c r="P229" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q229" s="2">
         <v>20374.5</v>
@@ -31426,7 +31426,7 @@
         <v>31</v>
       </c>
       <c r="P230" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q230" s="2">
         <v>18576.75</v>
@@ -31488,7 +31488,7 @@
         <v>36</v>
       </c>
       <c r="P231" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q231" s="2">
         <v>21573</v>
@@ -31550,7 +31550,7 @@
         <v>27</v>
       </c>
       <c r="P232" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q232" s="2">
         <v>16179.749999999998</v>
@@ -31612,7 +31612,7 @@
         <v>27</v>
       </c>
       <c r="P233" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q233" s="2">
         <v>16042.05</v>
@@ -31674,7 +31674,7 @@
         <v>30</v>
       </c>
       <c r="P234" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q234" s="2">
         <v>17824.5</v>
@@ -31736,7 +31736,7 @@
         <v>34</v>
       </c>
       <c r="P235" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q235" s="2">
         <v>20201.099999999999</v>
@@ -31798,7 +31798,7 @@
         <v>35</v>
       </c>
       <c r="P236" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q236" s="2">
         <v>20795.25</v>
@@ -31860,7 +31860,7 @@
         <v>34</v>
       </c>
       <c r="P237" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q237" s="2">
         <v>20201.099999999999</v>
@@ -31922,7 +31922,7 @@
         <v>30</v>
       </c>
       <c r="P238" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q238" s="2">
         <v>17824.5</v>
@@ -31984,7 +31984,7 @@
         <v>31</v>
       </c>
       <c r="P239" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q239" s="2">
         <v>18418.649999999998</v>
@@ -32046,7 +32046,7 @@
         <v>51</v>
       </c>
       <c r="P240" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q240" s="2">
         <v>30301.649999999998</v>
@@ -32108,7 +32108,7 @@
         <v>53</v>
       </c>
       <c r="P241" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q241" s="2">
         <v>31489.949999999997</v>
@@ -32170,7 +32170,7 @@
         <v>41</v>
       </c>
       <c r="P242" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q242" s="2">
         <v>24360.149999999998</v>
@@ -32232,7 +32232,7 @@
         <v>39</v>
       </c>
       <c r="P243" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q243" s="2">
         <v>23171.85</v>
@@ -32294,7 +32294,7 @@
         <v>38</v>
       </c>
       <c r="P244" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q244" s="2">
         <v>22577.699999999997</v>
@@ -32356,7 +32356,7 @@
         <v>46</v>
       </c>
       <c r="P245" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q245" s="2">
         <v>27330.899999999998</v>
@@ -32418,7 +32418,7 @@
         <v>38</v>
       </c>
       <c r="P246" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q246" s="2">
         <v>22577.699999999997</v>
@@ -32480,7 +32480,7 @@
         <v>28</v>
       </c>
       <c r="P247" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q247" s="2">
         <v>16636.199999999997</v>
@@ -32542,7 +32542,7 @@
         <v>34</v>
       </c>
       <c r="P248" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q248" s="2">
         <v>20201.099999999999</v>
@@ -32604,7 +32604,7 @@
         <v>32</v>
       </c>
       <c r="P249" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q249" s="2">
         <v>19012.8</v>
@@ -32666,7 +32666,7 @@
         <v>34</v>
       </c>
       <c r="P250" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q250" s="2">
         <v>20201.099999999999</v>
@@ -32728,7 +32728,7 @@
         <v>57</v>
       </c>
       <c r="P251" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q251" s="2">
         <v>33866.549999999996</v>
@@ -32790,7 +32790,7 @@
         <v>34</v>
       </c>
       <c r="P252" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q252" s="2">
         <v>20201.099999999999</v>
@@ -32852,7 +32852,7 @@
         <v>44</v>
       </c>
       <c r="P253" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q253" s="2">
         <v>26142.6</v>
@@ -32914,7 +32914,7 @@
         <v>33</v>
       </c>
       <c r="P254" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q254" s="2">
         <v>19606.949999999997</v>
@@ -32976,7 +32976,7 @@
         <v>37</v>
       </c>
       <c r="P255" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q255" s="2">
         <v>21983.55</v>
@@ -33038,7 +33038,7 @@
         <v>25</v>
       </c>
       <c r="P256" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q256" s="2">
         <v>14853.749999999998</v>
@@ -33100,7 +33100,7 @@
         <v>37</v>
       </c>
       <c r="P257" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q257" s="2">
         <v>21983.55</v>
@@ -33162,7 +33162,7 @@
         <v>24</v>
       </c>
       <c r="P258" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q258" s="2">
         <v>14259.599999999999</v>
@@ -33224,7 +33224,7 @@
         <v>61</v>
       </c>
       <c r="P259" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q259" s="2">
         <v>39820.799999999996</v>
@@ -33286,7 +33286,7 @@
         <v>34</v>
       </c>
       <c r="P260" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q260" s="2">
         <v>22195.199999999997</v>
@@ -33348,7 +33348,7 @@
         <v>36</v>
       </c>
       <c r="P261" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q261" s="2">
         <v>23500.799999999999</v>
@@ -33410,7 +33410,7 @@
         <v>35</v>
       </c>
       <c r="P262" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q262" s="2">
         <v>22848</v>
@@ -33472,7 +33472,7 @@
         <v>28</v>
       </c>
       <c r="P263" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q263" s="2">
         <v>18278.399999999998</v>
@@ -33534,7 +33534,7 @@
         <v>59</v>
       </c>
       <c r="P264" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q264" s="2">
         <v>38515.199999999997</v>
@@ -33596,7 +33596,7 @@
         <v>45</v>
       </c>
       <c r="P265" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q265" s="2">
         <v>29375.999999999996</v>
@@ -33658,7 +33658,7 @@
         <v>45</v>
       </c>
       <c r="P266" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q266" s="2">
         <v>29375.999999999996</v>
@@ -33720,7 +33720,7 @@
         <v>30</v>
       </c>
       <c r="P267" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q267" s="2">
         <v>19584</v>
@@ -33782,7 +33782,7 @@
         <v>44</v>
       </c>
       <c r="P268" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q268" s="2">
         <v>28723.199999999997</v>
@@ -33844,7 +33844,7 @@
         <v>35</v>
       </c>
       <c r="P269" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q269" s="2">
         <v>22848</v>
@@ -33906,7 +33906,7 @@
         <v>60</v>
       </c>
       <c r="P270" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q270" s="2">
         <v>39168</v>
@@ -33968,7 +33968,7 @@
         <v>47</v>
       </c>
       <c r="P271" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q271" s="2">
         <v>30681.599999999999</v>
@@ -34030,7 +34030,7 @@
         <v>38</v>
       </c>
       <c r="P272" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q272" s="2">
         <v>24806.399999999998</v>
@@ -34092,7 +34092,7 @@
         <v>34</v>
       </c>
       <c r="P273" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q273" s="2">
         <v>22108.5</v>
@@ -34154,7 +34154,7 @@
         <v>77</v>
       </c>
       <c r="P274" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q274" s="2">
         <v>50069.25</v>
@@ -34216,7 +34216,7 @@
         <v>35</v>
       </c>
       <c r="P275" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q275" s="2">
         <v>22758.75</v>
@@ -34278,7 +34278,7 @@
         <v>32</v>
       </c>
       <c r="P276" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q276" s="2">
         <v>20808</v>
@@ -34340,7 +34340,7 @@
         <v>47</v>
       </c>
       <c r="P277" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q277" s="2">
         <v>30561.749999999996</v>
@@ -34402,7 +34402,7 @@
         <v>25</v>
       </c>
       <c r="P278" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q278" s="2">
         <v>16256.249999999998</v>
@@ -34464,7 +34464,7 @@
         <v>34</v>
       </c>
       <c r="P279" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q279" s="2">
         <v>22021.8</v>
@@ -34526,7 +34526,7 @@
         <v>24</v>
       </c>
       <c r="P280" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q280" s="2">
         <v>15544.8</v>
@@ -34588,7 +34588,7 @@
         <v>45</v>
       </c>
       <c r="P281" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q281" s="2">
         <v>29146.499999999996</v>
@@ -34650,7 +34650,7 @@
         <v>34</v>
       </c>
       <c r="P282" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q282" s="2">
         <v>22021.8</v>
@@ -34712,7 +34712,7 @@
         <v>54</v>
       </c>
       <c r="P283" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q283" s="2">
         <v>34975.799999999996</v>
@@ -34774,7 +34774,7 @@
         <v>34</v>
       </c>
       <c r="P284" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q284" s="2">
         <v>22021.8</v>
@@ -34836,7 +34836,7 @@
         <v>26</v>
       </c>
       <c r="P285" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q285" s="2">
         <v>16840.199999999997</v>
@@ -34898,7 +34898,7 @@
         <v>28</v>
       </c>
       <c r="P286" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q286" s="2">
         <v>18135.599999999999</v>
@@ -34960,7 +34960,7 @@
         <v>34</v>
       </c>
       <c r="P287" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q287" s="2">
         <v>22021.8</v>
@@ -35022,7 +35022,7 @@
         <v>29</v>
       </c>
       <c r="P288" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q288" s="2">
         <v>18783.3</v>
@@ -35084,7 +35084,7 @@
         <v>47</v>
       </c>
       <c r="P289" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q289" s="2">
         <v>31280.85</v>
@@ -35146,7 +35146,7 @@
         <v>31</v>
       </c>
       <c r="P290" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q290" s="2">
         <v>20632.05</v>
@@ -35208,7 +35208,7 @@
         <v>35</v>
       </c>
       <c r="P291" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q291" s="2">
         <v>23294.25</v>
@@ -35270,7 +35270,7 @@
         <v>33</v>
       </c>
       <c r="P292" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q292" s="2">
         <v>21963.149999999998</v>
@@ -35332,7 +35332,7 @@
         <v>24</v>
       </c>
       <c r="P293" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q293" s="2">
         <v>13647.599999999999</v>
@@ -35394,7 +35394,7 @@
         <v>77</v>
       </c>
       <c r="P294" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q294" s="2">
         <v>43786.049999999996</v>
@@ -35456,7 +35456,7 @@
         <v>24</v>
       </c>
       <c r="P295" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q295" s="2">
         <v>13647.599999999999</v>
@@ -35518,7 +35518,7 @@
         <v>34</v>
       </c>
       <c r="P296" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q296" s="2">
         <v>19334.099999999999</v>
@@ -35580,7 +35580,7 @@
         <v>34</v>
       </c>
       <c r="P297" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q297" s="2">
         <v>19334.099999999999</v>
@@ -35642,7 +35642,7 @@
         <v>34</v>
       </c>
       <c r="P298" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q298" s="2">
         <v>19334.099999999999</v>
@@ -35704,7 +35704,7 @@
         <v>28</v>
       </c>
       <c r="P299" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q299" s="2">
         <v>15922.199999999999</v>
@@ -35766,7 +35766,7 @@
         <v>36</v>
       </c>
       <c r="P300" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q300" s="2">
         <v>20471.399999999998</v>
@@ -35828,7 +35828,7 @@
         <v>24</v>
       </c>
       <c r="P301" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q301" s="2">
         <v>13647.599999999999</v>
@@ -35890,7 +35890,7 @@
         <v>34</v>
       </c>
       <c r="P302" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q302" s="2">
         <v>19334.099999999999</v>
@@ -35952,7 +35952,7 @@
         <v>45</v>
       </c>
       <c r="P303" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q303" s="2">
         <v>25589.25</v>
@@ -36014,7 +36014,7 @@
         <v>51</v>
       </c>
       <c r="P304" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q304" s="2">
         <v>29001.149999999998</v>
@@ -36076,7 +36076,7 @@
         <v>52</v>
       </c>
       <c r="P305" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q305" s="2">
         <v>29569.8</v>
@@ -36138,7 +36138,7 @@
         <v>46</v>
       </c>
       <c r="P306" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q306" s="2">
         <v>26157.899999999998</v>
@@ -36200,7 +36200,7 @@
         <v>26</v>
       </c>
       <c r="P307" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q307" s="2">
         <v>14784.9</v>
@@ -36262,7 +36262,7 @@
         <v>34</v>
       </c>
       <c r="P308" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q308" s="2">
         <v>19334.099999999999</v>
@@ -36324,7 +36324,7 @@
         <v>52</v>
       </c>
       <c r="P309" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q309" s="2">
         <v>29569.8</v>
@@ -36386,7 +36386,7 @@
         <v>39</v>
       </c>
       <c r="P310" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q310" s="2">
         <v>22177.35</v>
@@ -36448,7 +36448,7 @@
         <v>54</v>
       </c>
       <c r="P311" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q311" s="2">
         <v>30707.1</v>
@@ -36510,7 +36510,7 @@
         <v>36</v>
       </c>
       <c r="P312" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q312" s="2">
         <v>20471.399999999998</v>
@@ -36572,7 +36572,7 @@
         <v>34</v>
       </c>
       <c r="P313" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q313" s="2">
         <v>19334.099999999999</v>
@@ -36634,7 +36634,7 @@
         <v>166</v>
       </c>
       <c r="P314" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q314" s="2">
         <v>94395.9</v>
@@ -36696,7 +36696,7 @@
         <v>34</v>
       </c>
       <c r="P315" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q315" s="2">
         <v>19334.099999999999</v>
@@ -36758,7 +36758,7 @@
         <v>33</v>
       </c>
       <c r="P316" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q316" s="2">
         <v>18765.449999999997</v>
@@ -36820,7 +36820,7 @@
         <v>34</v>
       </c>
       <c r="P317" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q317" s="2">
         <v>19334.099999999999</v>
@@ -36882,7 +36882,7 @@
         <v>26</v>
       </c>
       <c r="P318" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q318" s="2">
         <v>14784.9</v>
@@ -36944,7 +36944,7 @@
         <v>35</v>
       </c>
       <c r="P319" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q319" s="2">
         <v>19902.75</v>
@@ -37006,7 +37006,7 @@
         <v>46</v>
       </c>
       <c r="P320" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q320" s="2">
         <v>26157.899999999998</v>
@@ -37068,7 +37068,7 @@
         <v>30</v>
       </c>
       <c r="P321" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q321" s="2">
         <v>17059.5</v>
@@ -37130,7 +37130,7 @@
         <v>39</v>
       </c>
       <c r="P322" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q322" s="2">
         <v>22177.35</v>
@@ -37192,7 +37192,7 @@
         <v>32</v>
       </c>
       <c r="P323" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q323" s="2">
         <v>18196.8</v>
@@ -37254,7 +37254,7 @@
         <v>28</v>
       </c>
       <c r="P324" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q324" s="2">
         <v>15922.199999999999</v>
@@ -37316,7 +37316,7 @@
         <v>53</v>
       </c>
       <c r="P325" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q325" s="2">
         <v>30138.449999999997</v>
@@ -37378,7 +37378,7 @@
         <v>34</v>
       </c>
       <c r="P326" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q326" s="2">
         <v>19334.099999999999</v>
@@ -37440,7 +37440,7 @@
         <v>35</v>
       </c>
       <c r="P327" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q327" s="2">
         <v>19813.5</v>
@@ -37502,7 +37502,7 @@
         <v>34</v>
       </c>
       <c r="P328" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q328" s="2">
         <v>19247.399999999998</v>
@@ -37564,7 +37564,7 @@
         <v>34</v>
       </c>
       <c r="P329" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q329" s="2">
         <v>19247.399999999998</v>
@@ -37626,7 +37626,7 @@
         <v>58</v>
       </c>
       <c r="P330" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q330" s="2">
         <v>32833.799999999996</v>
@@ -37688,7 +37688,7 @@
         <v>37</v>
       </c>
       <c r="P331" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q331" s="2">
         <v>20945.699999999997</v>
@@ -37750,7 +37750,7 @@
         <v>39</v>
       </c>
       <c r="P332" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q332" s="2">
         <v>22077.899999999998</v>
@@ -37812,7 +37812,7 @@
         <v>37</v>
       </c>
       <c r="P333" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q333" s="2">
         <v>20945.699999999997</v>
@@ -37874,7 +37874,7 @@
         <v>41</v>
       </c>
       <c r="P334" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q334" s="2">
         <v>23210.1</v>
@@ -37936,7 +37936,7 @@
         <v>51</v>
       </c>
       <c r="P335" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q335" s="2">
         <v>28871.1</v>
@@ -37998,7 +37998,7 @@
         <v>61</v>
       </c>
       <c r="P336" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q336" s="2">
         <v>34532.1</v>
@@ -38060,7 +38060,7 @@
         <v>27</v>
       </c>
       <c r="P337" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q337" s="2">
         <v>15284.699999999999</v>
@@ -38122,7 +38122,7 @@
         <v>32</v>
       </c>
       <c r="P338" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q338" s="2">
         <v>18115.199999999997</v>
@@ -38184,7 +38184,7 @@
         <v>40</v>
       </c>
       <c r="P339" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q339" s="2">
         <v>22644</v>
@@ -38246,7 +38246,7 @@
         <v>36</v>
       </c>
       <c r="P340" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q340" s="2">
         <v>20379.599999999999</v>
@@ -38308,7 +38308,7 @@
         <v>53</v>
       </c>
       <c r="P341" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q341" s="2">
         <v>30003.3</v>
@@ -38370,7 +38370,7 @@
         <v>34</v>
       </c>
       <c r="P342" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q342" s="2">
         <v>19247.399999999998</v>
@@ -38432,7 +38432,7 @@
         <v>34</v>
       </c>
       <c r="P343" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q343" s="2">
         <v>19247.399999999998</v>
@@ -38494,7 +38494,7 @@
         <v>25</v>
       </c>
       <c r="P344" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q344" s="2">
         <v>14152.499999999998</v>
@@ -38556,7 +38556,7 @@
         <v>60</v>
       </c>
       <c r="P345" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q345" s="2">
         <v>33966</v>
@@ -38618,7 +38618,7 @@
         <v>35</v>
       </c>
       <c r="P346" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q346" s="2">
         <v>19813.5</v>
@@ -38680,7 +38680,7 @@
         <v>40</v>
       </c>
       <c r="P347" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q347" s="2">
         <v>22644</v>
@@ -38742,7 +38742,7 @@
         <v>37</v>
       </c>
       <c r="P348" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q348" s="2">
         <v>20945.699999999997</v>
@@ -38804,7 +38804,7 @@
         <v>35</v>
       </c>
       <c r="P349" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q349" s="2">
         <v>19813.5</v>
@@ -38866,7 +38866,7 @@
         <v>32</v>
       </c>
       <c r="P350" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q350" s="2">
         <v>18115.199999999997</v>
@@ -38928,7 +38928,7 @@
         <v>39</v>
       </c>
       <c r="P351" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q351" s="2">
         <v>22077.899999999998</v>
@@ -38990,7 +38990,7 @@
         <v>34</v>
       </c>
       <c r="P352" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q352" s="2">
         <v>19247.399999999998</v>
@@ -39052,7 +39052,7 @@
         <v>31</v>
       </c>
       <c r="P353" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q353" s="2">
         <v>17549.099999999999</v>
@@ -39114,7 +39114,7 @@
         <v>36</v>
       </c>
       <c r="P354" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q354" s="2">
         <v>20379.599999999999</v>
@@ -39176,7 +39176,7 @@
         <v>30</v>
       </c>
       <c r="P355" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q355" s="2">
         <v>16983</v>
@@ -39238,7 +39238,7 @@
         <v>24</v>
       </c>
       <c r="P356" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q356" s="2">
         <v>13586.4</v>
@@ -39300,7 +39300,7 @@
         <v>42</v>
       </c>
       <c r="P357" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q357" s="2">
         <v>23776.199999999997</v>
@@ -39362,7 +39362,7 @@
         <v>34</v>
       </c>
       <c r="P358" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q358" s="2">
         <v>19247.399999999998</v>
@@ -39424,7 +39424,7 @@
         <v>33</v>
       </c>
       <c r="P359" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q359" s="2">
         <v>18681.3</v>
@@ -39486,7 +39486,7 @@
         <v>24</v>
       </c>
       <c r="P360" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q360" s="2">
         <v>13586.4</v>
@@ -39548,7 +39548,7 @@
         <v>32</v>
       </c>
       <c r="P361" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q361" s="2">
         <v>18115.199999999997</v>
@@ -39610,7 +39610,7 @@
         <v>34</v>
       </c>
       <c r="P362" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q362" s="2">
         <v>19247.399999999998</v>
@@ -39672,7 +39672,7 @@
         <v>45</v>
       </c>
       <c r="P363" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q363" s="2">
         <v>25474.5</v>
@@ -39734,7 +39734,7 @@
         <v>34</v>
       </c>
       <c r="P364" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q364" s="2">
         <v>19247.399999999998</v>
@@ -39796,7 +39796,7 @@
         <v>39</v>
       </c>
       <c r="P365" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q365" s="2">
         <v>22077.899999999998</v>
@@ -39858,7 +39858,7 @@
         <v>150</v>
       </c>
       <c r="P366" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q366" s="2">
         <v>84915</v>
@@ -39920,7 +39920,7 @@
         <v>24</v>
       </c>
       <c r="P367" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q367" s="2">
         <v>13586.4</v>
@@ -39982,7 +39982,7 @@
         <v>26</v>
       </c>
       <c r="P368" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q368" s="2">
         <v>14652.3</v>
@@ -40044,7 +40044,7 @@
         <v>52</v>
       </c>
       <c r="P369" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q369" s="2">
         <v>29304.6</v>
@@ -40106,7 +40106,7 @@
         <v>73</v>
       </c>
       <c r="P370" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q370" s="2">
         <v>41139.149999999994</v>
@@ -40168,7 +40168,7 @@
         <v>90</v>
       </c>
       <c r="P371" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q371" s="2">
         <v>50719.5</v>
@@ -40230,7 +40230,7 @@
         <v>34</v>
       </c>
       <c r="P372" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q372" s="2">
         <v>19160.699999999997</v>
@@ -40292,7 +40292,7 @@
         <v>34</v>
       </c>
       <c r="P373" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q373" s="2">
         <v>19160.699999999997</v>
@@ -40354,7 +40354,7 @@
         <v>47</v>
       </c>
       <c r="P374" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q374" s="2">
         <v>26486.85</v>
@@ -40416,7 +40416,7 @@
         <v>27</v>
       </c>
       <c r="P375" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q375" s="2">
         <v>15215.849999999999</v>
@@ -40478,7 +40478,7 @@
         <v>37</v>
       </c>
       <c r="P376" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q376" s="2">
         <v>20851.349999999999</v>
@@ -40540,7 +40540,7 @@
         <v>28</v>
       </c>
       <c r="P377" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q377" s="2">
         <v>15779.4</v>
@@ -40602,7 +40602,7 @@
         <v>50</v>
       </c>
       <c r="P378" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q378" s="2">
         <v>28177.499999999996</v>
@@ -40664,7 +40664,7 @@
         <v>37</v>
       </c>
       <c r="P379" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q379" s="2">
         <v>20851.349999999999</v>
@@ -40726,7 +40726,7 @@
         <v>24</v>
       </c>
       <c r="P380" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q380" s="2">
         <v>13525.199999999999</v>
@@ -40788,7 +40788,7 @@
         <v>75</v>
       </c>
       <c r="P381" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q381" s="2">
         <v>42266.25</v>
@@ -40850,7 +40850,7 @@
         <v>31</v>
       </c>
       <c r="P382" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q382" s="2">
         <v>17470.05</v>
@@ -40912,7 +40912,7 @@
         <v>27</v>
       </c>
       <c r="P383" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q383" s="2">
         <v>15215.849999999999</v>
@@ -40974,7 +40974,7 @@
         <v>35</v>
       </c>
       <c r="P384" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q384" s="2">
         <v>19724.25</v>
@@ -41036,7 +41036,7 @@
         <v>36</v>
       </c>
       <c r="P385" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q385" s="2">
         <v>20287.8</v>
@@ -41098,7 +41098,7 @@
         <v>34</v>
       </c>
       <c r="P386" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q386" s="2">
         <v>19160.699999999997</v>
@@ -41160,7 +41160,7 @@
         <v>24</v>
       </c>
       <c r="P387" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q387" s="2">
         <v>13525.199999999999</v>
@@ -41222,7 +41222,7 @@
         <v>30</v>
       </c>
       <c r="P388" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q388" s="2">
         <v>16906.5</v>
@@ -41284,7 +41284,7 @@
         <v>42</v>
       </c>
       <c r="P389" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q389" s="2">
         <v>23669.1</v>
@@ -41346,7 +41346,7 @@
         <v>33</v>
       </c>
       <c r="P390" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q390" s="2">
         <v>18597.149999999998</v>
@@ -41408,7 +41408,7 @@
         <v>49</v>
       </c>
       <c r="P391" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q391" s="2">
         <v>27488.999999999996</v>
@@ -41470,7 +41470,7 @@
         <v>53</v>
       </c>
       <c r="P392" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q392" s="2">
         <v>29868.149999999998</v>
@@ -41532,7 +41532,7 @@
         <v>25</v>
       </c>
       <c r="P393" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q393" s="2">
         <v>14088.749999999998</v>
@@ -41594,7 +41594,7 @@
         <v>46</v>
       </c>
       <c r="P394" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q394" s="2">
         <v>25923.3</v>
@@ -41656,7 +41656,7 @@
         <v>34</v>
       </c>
       <c r="P395" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q395" s="2">
         <v>19160.699999999997</v>
@@ -41718,7 +41718,7 @@
         <v>27</v>
       </c>
       <c r="P396" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q396" s="2">
         <v>15215.849999999999</v>
@@ -41780,7 +41780,7 @@
         <v>44</v>
       </c>
       <c r="P397" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q397" s="2">
         <v>24796.199999999997</v>
@@ -41842,7 +41842,7 @@
         <v>35</v>
       </c>
       <c r="P398" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q398" s="2">
         <v>19724.25</v>
@@ -41904,7 +41904,7 @@
         <v>42</v>
       </c>
       <c r="P399" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q399" s="2">
         <v>23669.1</v>
@@ -41966,7 +41966,7 @@
         <v>24</v>
       </c>
       <c r="P400" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q400" s="2">
         <v>13525.199999999999</v>
@@ -42028,7 +42028,7 @@
         <v>49</v>
       </c>
       <c r="P401" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q401" s="2">
         <v>27488.999999999996</v>
@@ -42090,7 +42090,7 @@
         <v>25</v>
       </c>
       <c r="P402" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q402" s="2">
         <v>14088.749999999998</v>
@@ -42152,7 +42152,7 @@
         <v>45</v>
       </c>
       <c r="P403" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q403" s="2">
         <v>25359.75</v>
@@ -42214,7 +42214,7 @@
         <v>39</v>
       </c>
       <c r="P404" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q404" s="2">
         <v>21978.449999999997</v>
@@ -42276,7 +42276,7 @@
         <v>26</v>
       </c>
       <c r="P405" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q405" s="2">
         <v>14652.3</v>
@@ -42338,7 +42338,7 @@
         <v>31</v>
       </c>
       <c r="P406" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q406" s="2">
         <v>17470.05</v>
@@ -42400,7 +42400,7 @@
         <v>40</v>
       </c>
       <c r="P407" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q407" s="2">
         <v>22542</v>
@@ -42462,7 +42462,7 @@
         <v>27</v>
       </c>
       <c r="P408" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q408" s="2">
         <v>15215.849999999999</v>
@@ -42524,7 +42524,7 @@
         <v>34</v>
       </c>
       <c r="P409" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q409" s="2">
         <v>19160.699999999997</v>
@@ -42586,7 +42586,7 @@
         <v>76</v>
       </c>
       <c r="P410" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q410" s="2">
         <v>42829.799999999996</v>
@@ -42648,7 +42648,7 @@
         <v>46</v>
       </c>
       <c r="P411" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q411" s="2">
         <v>25806</v>
@@ -42710,7 +42710,7 @@
         <v>42</v>
       </c>
       <c r="P412" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q412" s="2">
         <v>23454.899999999998</v>
@@ -42772,7 +42772,7 @@
         <v>25</v>
       </c>
       <c r="P413" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q413" s="2">
         <v>14024.999999999998</v>
@@ -42834,7 +42834,7 @@
         <v>48</v>
       </c>
       <c r="P414" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q414" s="2">
         <v>26927.999999999996</v>
@@ -42896,7 +42896,7 @@
         <v>34</v>
       </c>
       <c r="P415" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q415" s="2">
         <v>19074</v>
@@ -42958,7 +42958,7 @@
         <v>28</v>
       </c>
       <c r="P416" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q416" s="2">
         <v>15707.999999999998</v>
@@ -43020,7 +43020,7 @@
         <v>37</v>
       </c>
       <c r="P417" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q417" s="2">
         <v>20757</v>
@@ -43082,7 +43082,7 @@
         <v>34</v>
       </c>
       <c r="P418" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q418" s="2">
         <v>19074</v>
@@ -43144,7 +43144,7 @@
         <v>38</v>
       </c>
       <c r="P419" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q419" s="2">
         <v>21318</v>
@@ -43206,7 +43206,7 @@
         <v>36</v>
       </c>
       <c r="P420" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q420" s="2">
         <v>20196</v>
@@ -43268,7 +43268,7 @@
         <v>28</v>
       </c>
       <c r="P421" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q421" s="2">
         <v>15707.999999999998</v>
@@ -43330,7 +43330,7 @@
         <v>34</v>
       </c>
       <c r="P422" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q422" s="2">
         <v>19074</v>
@@ -43392,7 +43392,7 @@
         <v>31</v>
       </c>
       <c r="P423" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q423" s="2">
         <v>17391</v>
@@ -43454,7 +43454,7 @@
         <v>42</v>
       </c>
       <c r="P424" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q424" s="2">
         <v>23562</v>
@@ -43516,7 +43516,7 @@
         <v>34</v>
       </c>
       <c r="P425" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q425" s="2">
         <v>18987.3</v>
@@ -43578,7 +43578,7 @@
         <v>63</v>
       </c>
       <c r="P426" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q426" s="2">
         <v>35343</v>
@@ -43640,7 +43640,7 @@
         <v>34</v>
       </c>
       <c r="P427" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q427" s="2">
         <v>19074</v>
@@ -43702,7 +43702,7 @@
         <v>37</v>
       </c>
       <c r="P428" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q428" s="2">
         <v>20662.649999999998</v>
@@ -43764,7 +43764,7 @@
         <v>39</v>
       </c>
       <c r="P429" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q429" s="2">
         <v>21779.55</v>
@@ -43826,7 +43826,7 @@
         <v>38</v>
       </c>
       <c r="P430" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q430" s="2">
         <v>21221.1</v>
@@ -43888,7 +43888,7 @@
         <v>41</v>
       </c>
       <c r="P431" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q431" s="2">
         <v>22896.449999999997</v>
@@ -43950,7 +43950,7 @@
         <v>38</v>
       </c>
       <c r="P432" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q432" s="2">
         <v>21221.1</v>
@@ -44012,7 +44012,7 @@
         <v>27</v>
       </c>
       <c r="P433" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q433" s="2">
         <v>15078.15</v>
@@ -44074,7 +44074,7 @@
         <v>39</v>
       </c>
       <c r="P434" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q434" s="2">
         <v>21779.55</v>
@@ -44136,7 +44136,7 @@
         <v>31</v>
       </c>
       <c r="P435" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q435" s="2">
         <v>17074.8</v>
@@ -44198,7 +44198,7 @@
         <v>24</v>
       </c>
       <c r="P436" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q436" s="2">
         <v>13219.199999999999</v>
@@ -44260,7 +44260,7 @@
         <v>35</v>
       </c>
       <c r="P437" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q437" s="2">
         <v>19278</v>
@@ -44322,7 +44322,7 @@
         <v>50</v>
       </c>
       <c r="P438" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q438" s="2">
         <v>27539.999999999996</v>
@@ -44384,7 +44384,7 @@
         <v>51</v>
       </c>
       <c r="P439" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q439" s="2">
         <v>28090.799999999999</v>
@@ -44446,7 +44446,7 @@
         <v>31</v>
       </c>
       <c r="P440" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q440" s="2">
         <v>17074.8</v>
@@ -44508,7 +44508,7 @@
         <v>32</v>
       </c>
       <c r="P441" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q441" s="2">
         <v>17625.599999999999</v>
@@ -44570,7 +44570,7 @@
         <v>38</v>
       </c>
       <c r="P442" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q442" s="2">
         <v>20930.399999999998</v>
@@ -44632,7 +44632,7 @@
         <v>37</v>
       </c>
       <c r="P443" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q443" s="2">
         <v>20379.599999999999</v>
@@ -44694,7 +44694,7 @@
         <v>34</v>
       </c>
       <c r="P444" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q444" s="2">
         <v>18727.199999999997</v>
@@ -44756,7 +44756,7 @@
         <v>33</v>
       </c>
       <c r="P445" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q445" s="2">
         <v>18176.399999999998</v>
@@ -44818,7 +44818,7 @@
         <v>34</v>
       </c>
       <c r="P446" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q446" s="2">
         <v>18727.199999999997</v>
@@ -44880,7 +44880,7 @@
         <v>36</v>
       </c>
       <c r="P447" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q447" s="2">
         <v>19828.8</v>
@@ -44942,7 +44942,7 @@
         <v>46</v>
       </c>
       <c r="P448" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q448" s="2">
         <v>25336.799999999999</v>
@@ -45004,7 +45004,7 @@
         <v>34</v>
       </c>
       <c r="P449" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q449" s="2">
         <v>18727.199999999997</v>
@@ -45066,7 +45066,7 @@
         <v>41</v>
       </c>
       <c r="P450" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q450" s="2">
         <v>22478.25</v>
@@ -45128,7 +45128,7 @@
         <v>35</v>
       </c>
       <c r="P451" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q451" s="2">
         <v>19188.75</v>
@@ -45190,7 +45190,7 @@
         <v>49</v>
       </c>
       <c r="P452" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q452" s="2">
         <v>26864.249999999996</v>
@@ -45252,7 +45252,7 @@
         <v>29</v>
       </c>
       <c r="P453" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q453" s="2">
         <v>15899.249999999998</v>
@@ -45314,7 +45314,7 @@
         <v>34</v>
       </c>
       <c r="P454" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q454" s="2">
         <v>18640.5</v>
@@ -45376,7 +45376,7 @@
         <v>24</v>
       </c>
       <c r="P455" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q455" s="2">
         <v>13157.999999999998</v>
@@ -45438,7 +45438,7 @@
         <v>28</v>
       </c>
       <c r="P456" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q456" s="2">
         <v>15350.999999999998</v>
@@ -45500,7 +45500,7 @@
         <v>35</v>
       </c>
       <c r="P457" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q457" s="2">
         <v>19188.75</v>
@@ -45562,7 +45562,7 @@
         <v>32</v>
       </c>
       <c r="P458" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q458" s="2">
         <v>17544</v>
@@ -45624,7 +45624,7 @@
         <v>39</v>
       </c>
       <c r="P459" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q459" s="2">
         <v>21381.75</v>
@@ -45686,7 +45686,7 @@
         <v>34</v>
       </c>
       <c r="P460" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q460" s="2">
         <v>18640.5</v>
@@ -45748,7 +45748,7 @@
         <v>25</v>
       </c>
       <c r="P461" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q461" s="2">
         <v>13706.249999999998</v>
@@ -45810,7 +45810,7 @@
         <v>25</v>
       </c>
       <c r="P462" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q462" s="2">
         <v>13706.249999999998</v>
@@ -45872,7 +45872,7 @@
         <v>36</v>
       </c>
       <c r="P463" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q463" s="2">
         <v>19737</v>
@@ -45934,7 +45934,7 @@
         <v>38</v>
       </c>
       <c r="P464" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q464" s="2">
         <v>20833.5</v>
@@ -45996,7 +45996,7 @@
         <v>24</v>
       </c>
       <c r="P465" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q465" s="2">
         <v>13157.999999999998</v>
@@ -46058,7 +46058,7 @@
         <v>31</v>
       </c>
       <c r="P466" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q466" s="2">
         <v>18181.5</v>
@@ -46120,7 +46120,7 @@
         <v>31</v>
       </c>
       <c r="P467" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q467" s="2">
         <v>18181.5</v>
@@ -46182,7 +46182,7 @@
         <v>25</v>
       </c>
       <c r="P468" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q468" s="2">
         <v>14662.499999999998</v>
@@ -46244,7 +46244,7 @@
         <v>39</v>
       </c>
       <c r="P469" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q469" s="2">
         <v>22873.5</v>
@@ -46306,7 +46306,7 @@
         <v>46</v>
       </c>
       <c r="P470" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q470" s="2">
         <v>26978.999999999996</v>
@@ -46368,7 +46368,7 @@
         <v>34</v>
       </c>
       <c r="P471" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q471" s="2">
         <v>19941</v>
@@ -46430,7 +46430,7 @@
         <v>36</v>
       </c>
       <c r="P472" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q472" s="2">
         <v>21114</v>
@@ -46492,7 +46492,7 @@
         <v>46</v>
       </c>
       <c r="P473" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q473" s="2">
         <v>26978.999999999996</v>
@@ -46554,7 +46554,7 @@
         <v>34</v>
       </c>
       <c r="P474" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q474" s="2">
         <v>19941</v>
@@ -46616,7 +46616,7 @@
         <v>39</v>
       </c>
       <c r="P475" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q475" s="2">
         <v>22873.5</v>
@@ -46678,7 +46678,7 @@
         <v>25</v>
       </c>
       <c r="P476" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q476" s="2">
         <v>14662.499999999998</v>
@@ -46740,7 +46740,7 @@
         <v>38</v>
       </c>
       <c r="P477" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q477" s="2">
         <v>22287</v>
@@ -46802,7 +46802,7 @@
         <v>38</v>
       </c>
       <c r="P478" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q478" s="2">
         <v>22287</v>
@@ -46864,7 +46864,7 @@
         <v>72</v>
       </c>
       <c r="P479" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q479" s="2">
         <v>42228</v>
@@ -46926,7 +46926,7 @@
         <v>26</v>
       </c>
       <c r="P480" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q480" s="2">
         <v>15248.999999999998</v>
@@ -46988,7 +46988,7 @@
         <v>40</v>
       </c>
       <c r="P481" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q481" s="2">
         <v>23460</v>
@@ -47050,7 +47050,7 @@
         <v>34</v>
       </c>
       <c r="P482" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q482" s="2">
         <v>19941</v>
@@ -47112,7 +47112,7 @@
         <v>34</v>
       </c>
       <c r="P483" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q483" s="2">
         <v>19941</v>
@@ -47174,7 +47174,7 @@
         <v>40</v>
       </c>
       <c r="P484" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q484" s="2">
         <v>23460</v>
@@ -47236,7 +47236,7 @@
         <v>28</v>
       </c>
       <c r="P485" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q485" s="2">
         <v>16422</v>
@@ -47298,7 +47298,7 @@
         <v>46</v>
       </c>
       <c r="P486" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q486" s="2">
         <v>26978.999999999996</v>
@@ -47360,7 +47360,7 @@
         <v>31</v>
       </c>
       <c r="P487" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q487" s="2">
         <v>18181.5</v>
@@ -47422,7 +47422,7 @@
         <v>44</v>
       </c>
       <c r="P488" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q488" s="2">
         <v>25806</v>
@@ -47484,7 +47484,7 @@
         <v>37</v>
       </c>
       <c r="P489" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q489" s="2">
         <v>21700.5</v>
@@ -47546,7 +47546,7 @@
         <v>24</v>
       </c>
       <c r="P490" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q490" s="2">
         <v>14075.999999999998</v>
@@ -47608,7 +47608,7 @@
         <v>33</v>
       </c>
       <c r="P491" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q491" s="2">
         <v>19354.5</v>
@@ -47670,7 +47670,7 @@
         <v>34</v>
       </c>
       <c r="P492" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q492" s="2">
         <v>19941</v>
@@ -47732,7 +47732,7 @@
         <v>34</v>
       </c>
       <c r="P493" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q493" s="2">
         <v>19941</v>
@@ -47794,7 +47794,7 @@
         <v>39</v>
       </c>
       <c r="P494" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q494" s="2">
         <v>22873.5</v>
@@ -47856,7 +47856,7 @@
         <v>27</v>
       </c>
       <c r="P495" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q495" s="2">
         <v>15835.499999999998</v>
@@ -47918,7 +47918,7 @@
         <v>31</v>
       </c>
       <c r="P496" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q496" s="2">
         <v>18181.5</v>
@@ -47980,7 +47980,7 @@
         <v>25</v>
       </c>
       <c r="P497" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q497" s="2">
         <v>14662.499999999998</v>
@@ -48042,7 +48042,7 @@
         <v>24</v>
       </c>
       <c r="P498" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q498" s="2">
         <v>14075.999999999998</v>
@@ -48104,7 +48104,7 @@
         <v>31</v>
       </c>
       <c r="P499" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q499" s="2">
         <v>18181.5</v>
@@ -48166,7 +48166,7 @@
         <v>24</v>
       </c>
       <c r="P500" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q500" s="2">
         <v>14075.999999999998</v>
@@ -48228,7 +48228,7 @@
         <v>27</v>
       </c>
       <c r="P501" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q501" s="2">
         <v>15835.499999999998</v>
@@ -48290,7 +48290,7 @@
         <v>32</v>
       </c>
       <c r="P502" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q502" s="2">
         <v>17462.399999999998</v>
@@ -48352,7 +48352,7 @@
         <v>85</v>
       </c>
       <c r="P503" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q503" s="2">
         <v>46384.5</v>
@@ -48414,7 +48414,7 @@
         <v>34</v>
       </c>
       <c r="P504" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q504" s="2">
         <v>18553.8</v>
@@ -48476,7 +48476,7 @@
         <v>34</v>
       </c>
       <c r="P505" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q505" s="2">
         <v>18553.8</v>
@@ -48538,7 +48538,7 @@
         <v>38</v>
       </c>
       <c r="P506" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q506" s="2">
         <v>20736.599999999999</v>
@@ -48600,7 +48600,7 @@
         <v>43</v>
       </c>
       <c r="P507" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q507" s="2">
         <v>23465.1</v>
@@ -48662,7 +48662,7 @@
         <v>45</v>
       </c>
       <c r="P508" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q508" s="2">
         <v>24556.5</v>
@@ -48724,7 +48724,7 @@
         <v>41</v>
       </c>
       <c r="P509" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q509" s="2">
         <v>22373.699999999997</v>
@@ -48786,7 +48786,7 @@
         <v>30</v>
       </c>
       <c r="P510" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q510" s="2">
         <v>16370.999999999998</v>
@@ -48848,7 +48848,7 @@
         <v>25</v>
       </c>
       <c r="P511" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q511" s="2">
         <v>13642.499999999998</v>
@@ -48910,7 +48910,7 @@
         <v>45</v>
       </c>
       <c r="P512" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q512" s="2">
         <v>24556.5</v>
@@ -48972,7 +48972,7 @@
         <v>31</v>
       </c>
       <c r="P513" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q513" s="2">
         <v>16916.699999999997</v>
@@ -49034,7 +49034,7 @@
         <v>25</v>
       </c>
       <c r="P514" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q514" s="2">
         <v>13642.499999999998</v>
@@ -49096,7 +49096,7 @@
         <v>34</v>
       </c>
       <c r="P515" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q515" s="2">
         <v>18553.8</v>
@@ -49158,7 +49158,7 @@
         <v>25</v>
       </c>
       <c r="P516" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q516" s="2">
         <v>13642.499999999998</v>
@@ -49220,7 +49220,7 @@
         <v>38</v>
       </c>
       <c r="P517" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q517" s="2">
         <v>20736.599999999999</v>
@@ -49282,7 +49282,7 @@
         <v>34</v>
       </c>
       <c r="P518" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q518" s="2">
         <v>18553.8</v>
@@ -49344,7 +49344,7 @@
         <v>37</v>
       </c>
       <c r="P519" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q519" s="2">
         <v>20190.899999999998</v>
@@ -49406,7 +49406,7 @@
         <v>28</v>
       </c>
       <c r="P520" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q520" s="2">
         <v>15279.599999999999</v>
@@ -49468,7 +49468,7 @@
         <v>44</v>
       </c>
       <c r="P521" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q521" s="2">
         <v>24010.799999999999</v>
@@ -49530,7 +49530,7 @@
         <v>34</v>
       </c>
       <c r="P522" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q522" s="2">
         <v>18553.8</v>
@@ -49592,7 +49592,7 @@
         <v>32</v>
       </c>
       <c r="P523" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q523" s="2">
         <v>17462.399999999998</v>
@@ -49654,7 +49654,7 @@
         <v>46</v>
       </c>
       <c r="P524" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q524" s="2">
         <v>25102.199999999997</v>
@@ -49716,7 +49716,7 @@
         <v>51</v>
       </c>
       <c r="P525" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q525" s="2">
         <v>27830.699999999997</v>
@@ -49778,7 +49778,7 @@
         <v>50</v>
       </c>
       <c r="P526" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q526" s="2">
         <v>27284.999999999996</v>
@@ -49840,7 +49840,7 @@
         <v>27</v>
       </c>
       <c r="P527" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q527" s="2">
         <v>14733.9</v>
@@ -49902,7 +49902,7 @@
         <v>37</v>
       </c>
       <c r="P528" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q528" s="2">
         <v>20190.899999999998</v>
@@ -49964,7 +49964,7 @@
         <v>35</v>
       </c>
       <c r="P529" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q529" s="2">
         <v>19099.5</v>
@@ -50026,7 +50026,7 @@
         <v>60</v>
       </c>
       <c r="P530" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q530" s="2">
         <v>32588.999999999996</v>
@@ -50088,7 +50088,7 @@
         <v>41</v>
       </c>
       <c r="P531" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q531" s="2">
         <v>22269.149999999998</v>
@@ -50150,7 +50150,7 @@
         <v>50</v>
       </c>
       <c r="P532" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q532" s="2">
         <v>27157.499999999996</v>
@@ -50212,7 +50212,7 @@
         <v>49</v>
       </c>
       <c r="P533" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q533" s="2">
         <v>26614.35</v>
@@ -50274,7 +50274,7 @@
         <v>47</v>
       </c>
       <c r="P534" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q534" s="2">
         <v>25528.05</v>
@@ -50336,7 +50336,7 @@
         <v>65</v>
       </c>
       <c r="P535" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q535" s="2">
         <v>35304.75</v>
@@ -50398,7 +50398,7 @@
         <v>32</v>
       </c>
       <c r="P536" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q536" s="2">
         <v>17380.8</v>
@@ -50460,7 +50460,7 @@
         <v>30</v>
       </c>
       <c r="P537" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q537" s="2">
         <v>16294.499999999998</v>
@@ -50522,7 +50522,7 @@
         <v>34</v>
       </c>
       <c r="P538" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q538" s="2">
         <v>18467.099999999999</v>
@@ -50584,7 +50584,7 @@
         <v>25</v>
       </c>
       <c r="P539" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q539" s="2">
         <v>14471.249999999998</v>
@@ -50646,7 +50646,7 @@
         <v>24</v>
       </c>
       <c r="P540" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q540" s="2">
         <v>13892.4</v>
@@ -50708,7 +50708,7 @@
         <v>34</v>
       </c>
       <c r="P541" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q541" s="2">
         <v>19680.899999999998</v>
@@ -50770,7 +50770,7 @@
         <v>43</v>
       </c>
       <c r="P542" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q542" s="2">
         <v>24890.55</v>
@@ -50832,7 +50832,7 @@
         <v>29</v>
       </c>
       <c r="P543" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q543" s="2">
         <v>16786.649999999998</v>
@@ -50894,7 +50894,7 @@
         <v>25</v>
       </c>
       <c r="P544" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q544" s="2">
         <v>14471.249999999998</v>
@@ -50956,7 +50956,7 @@
         <v>38</v>
       </c>
       <c r="P545" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q545" s="2">
         <v>21996.3</v>
@@ -51018,7 +51018,7 @@
         <v>34</v>
       </c>
       <c r="P546" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q546" s="2">
         <v>19680.899999999998</v>
@@ -51080,7 +51080,7 @@
         <v>31</v>
       </c>
       <c r="P547" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q547" s="2">
         <v>17944.349999999999</v>
@@ -51142,7 +51142,7 @@
         <v>45</v>
       </c>
       <c r="P548" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q548" s="2">
         <v>26048.25</v>
@@ -51204,7 +51204,7 @@
         <v>38</v>
       </c>
       <c r="P549" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q549" s="2">
         <v>21996.3</v>
@@ -51266,7 +51266,7 @@
         <v>38</v>
       </c>
       <c r="P550" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q550" s="2">
         <v>21996.3</v>
@@ -51328,7 +51328,7 @@
         <v>44</v>
       </c>
       <c r="P551" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q551" s="2">
         <v>25469.399999999998</v>
@@ -51390,7 +51390,7 @@
         <v>24</v>
       </c>
       <c r="P552" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q552" s="2">
         <v>13892.4</v>
@@ -51452,7 +51452,7 @@
         <v>28</v>
       </c>
       <c r="P553" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q553" s="2">
         <v>16207.8</v>
@@ -51514,7 +51514,7 @@
         <v>27</v>
       </c>
       <c r="P554" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q554" s="2">
         <v>15628.949999999999</v>
@@ -51576,7 +51576,7 @@
         <v>187</v>
       </c>
       <c r="P555" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q555" s="2">
         <v>108244.95</v>
@@ -51638,7 +51638,7 @@
         <v>73</v>
       </c>
       <c r="P556" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q556" s="2">
         <v>42256.049999999996</v>
@@ -51700,7 +51700,7 @@
         <v>47</v>
       </c>
       <c r="P557" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q557" s="2">
         <v>27205.949999999997</v>
@@ -51762,7 +51762,7 @@
         <v>27</v>
       </c>
       <c r="P558" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q558" s="2">
         <v>15628.949999999999</v>
@@ -51824,7 +51824,7 @@
         <v>34</v>
       </c>
       <c r="P559" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q559" s="2">
         <v>19680.899999999998</v>
@@ -51886,7 +51886,7 @@
         <v>55</v>
       </c>
       <c r="P560" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q560" s="2">
         <v>31836.749999999996</v>
@@ -51948,7 +51948,7 @@
         <v>40</v>
       </c>
       <c r="P561" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q561" s="2">
         <v>23154</v>
@@ -52010,7 +52010,7 @@
         <v>44</v>
       </c>
       <c r="P562" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q562" s="2">
         <v>25469.399999999998</v>
@@ -52072,7 +52072,7 @@
         <v>36</v>
       </c>
       <c r="P563" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q563" s="2">
         <v>20838.599999999999</v>
@@ -52134,7 +52134,7 @@
         <v>26</v>
       </c>
       <c r="P564" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q564" s="2">
         <v>15050.099999999999</v>
@@ -52196,7 +52196,7 @@
         <v>25</v>
       </c>
       <c r="P565" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q565" s="2">
         <v>14471.249999999998</v>
@@ -52258,7 +52258,7 @@
         <v>25</v>
       </c>
       <c r="P566" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q566" s="2">
         <v>14471.249999999998</v>
@@ -52320,7 +52320,7 @@
         <v>30</v>
       </c>
       <c r="P567" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q567" s="2">
         <v>17365.5</v>
@@ -52382,7 +52382,7 @@
         <v>39</v>
       </c>
       <c r="P568" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q568" s="2">
         <v>22575.149999999998</v>
@@ -52444,7 +52444,7 @@
         <v>41</v>
       </c>
       <c r="P569" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q569" s="2">
         <v>23628.3</v>
@@ -52506,7 +52506,7 @@
         <v>51</v>
       </c>
       <c r="P570" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q570" s="2">
         <v>29391.3</v>
@@ -52568,7 +52568,7 @@
         <v>25</v>
       </c>
       <c r="P571" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q571" s="2">
         <v>14407.499999999998</v>
@@ -52630,7 +52630,7 @@
         <v>39</v>
       </c>
       <c r="P572" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q572" s="2">
         <v>22475.699999999997</v>
@@ -52692,7 +52692,7 @@
         <v>24</v>
       </c>
       <c r="P573" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q573" s="2">
         <v>13831.199999999999</v>
@@ -52754,7 +52754,7 @@
         <v>42</v>
       </c>
       <c r="P574" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q574" s="2">
         <v>24204.6</v>
@@ -52816,7 +52816,7 @@
         <v>34</v>
       </c>
       <c r="P575" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q575" s="2">
         <v>19594.199999999997</v>
@@ -52878,7 +52878,7 @@
         <v>34</v>
       </c>
       <c r="P576" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q576" s="2">
         <v>19594.199999999997</v>
@@ -52940,7 +52940,7 @@
         <v>38</v>
       </c>
       <c r="P577" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q577" s="2">
         <v>21899.399999999998</v>
@@ -53002,7 +53002,7 @@
         <v>38</v>
       </c>
       <c r="P578" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q578" s="2">
         <v>21899.399999999998</v>
@@ -53064,7 +53064,7 @@
         <v>33</v>
       </c>
       <c r="P579" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q579" s="2">
         <v>19017.899999999998</v>
@@ -53126,7 +53126,7 @@
         <v>31</v>
       </c>
       <c r="P580" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q580" s="2">
         <v>17865.3</v>
@@ -53188,7 +53188,7 @@
         <v>52</v>
       </c>
       <c r="P581" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q581" s="2">
         <v>29967.599999999999</v>
@@ -53250,7 +53250,7 @@
         <v>30</v>
       </c>
       <c r="P582" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q582" s="2">
         <v>17289</v>
@@ -53312,7 +53312,7 @@
         <v>24</v>
       </c>
       <c r="P583" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q583" s="2">
         <v>13831.199999999999</v>
@@ -53374,7 +53374,7 @@
         <v>51</v>
       </c>
       <c r="P584" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q584" s="2">
         <v>29391.3</v>
@@ -53436,7 +53436,7 @@
         <v>47</v>
       </c>
       <c r="P585" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q585" s="2">
         <v>27086.1</v>
@@ -53498,7 +53498,7 @@
         <v>38</v>
       </c>
       <c r="P586" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q586" s="2">
         <v>21899.399999999998</v>
@@ -53560,7 +53560,7 @@
         <v>27</v>
       </c>
       <c r="P587" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q587" s="2">
         <v>15560.099999999999</v>
@@ -53622,7 +53622,7 @@
         <v>25</v>
       </c>
       <c r="P588" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q588" s="2">
         <v>14407.499999999998</v>
@@ -53684,7 +53684,7 @@
         <v>30</v>
       </c>
       <c r="P589" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q589" s="2">
         <v>17289</v>
@@ -53746,7 +53746,7 @@
         <v>30</v>
       </c>
       <c r="P590" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q590" s="2">
         <v>17289</v>
@@ -53808,7 +53808,7 @@
         <v>52</v>
       </c>
       <c r="P591" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q591" s="2">
         <v>29967.599999999999</v>
@@ -53870,7 +53870,7 @@
         <v>33</v>
       </c>
       <c r="P592" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q592" s="2">
         <v>19017.899999999998</v>
@@ -53932,7 +53932,7 @@
         <v>34</v>
       </c>
       <c r="P593" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q593" s="2">
         <v>19594.199999999997</v>
@@ -53994,7 +53994,7 @@
         <v>39</v>
       </c>
       <c r="P594" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q594" s="2">
         <v>22475.699999999997</v>
@@ -54056,7 +54056,7 @@
         <v>45</v>
       </c>
       <c r="P595" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q595" s="2">
         <v>25933.5</v>
@@ -54118,7 +54118,7 @@
         <v>24</v>
       </c>
       <c r="P596" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q596" s="2">
         <v>13831.199999999999</v>
@@ -54180,7 +54180,7 @@
         <v>41</v>
       </c>
       <c r="P597" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q597" s="2">
         <v>23628.3</v>
@@ -54242,7 +54242,7 @@
         <v>34</v>
       </c>
       <c r="P598" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q598" s="2">
         <v>19594.199999999997</v>
@@ -54304,7 +54304,7 @@
         <v>34</v>
       </c>
       <c r="P599" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q599" s="2">
         <v>19594.199999999997</v>
@@ -54366,7 +54366,7 @@
         <v>60</v>
       </c>
       <c r="P600" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q600" s="2">
         <v>34578</v>
@@ -54428,7 +54428,7 @@
         <v>39</v>
       </c>
       <c r="P601" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q601" s="2">
         <v>22475.699999999997</v>
@@ -54490,7 +54490,7 @@
         <v>45</v>
       </c>
       <c r="P602" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q602" s="2">
         <v>25933.5</v>
@@ -54552,7 +54552,7 @@
         <v>27</v>
       </c>
       <c r="P603" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q603" s="2">
         <v>15560.099999999999</v>
@@ -54614,7 +54614,7 @@
         <v>25</v>
       </c>
       <c r="P604" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q604" s="2">
         <v>14407.499999999998</v>
@@ -54676,7 +54676,7 @@
         <v>40</v>
       </c>
       <c r="P605" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q605" s="2">
         <v>23052</v>
@@ -54738,7 +54738,7 @@
         <v>46</v>
       </c>
       <c r="P606" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q606" s="2">
         <v>26509.8</v>
@@ -54800,7 +54800,7 @@
         <v>58</v>
       </c>
       <c r="P607" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q607" s="2">
         <v>33425.399999999994</v>
@@ -54862,7 +54862,7 @@
         <v>46</v>
       </c>
       <c r="P608" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q608" s="2">
         <v>26509.8</v>
@@ -54924,7 +54924,7 @@
         <v>50</v>
       </c>
       <c r="P609" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q609" s="2">
         <v>28814.999999999996</v>
@@ -54986,7 +54986,7 @@
         <v>28</v>
       </c>
       <c r="P610" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q610" s="2">
         <v>16136.4</v>
@@ -55048,7 +55048,7 @@
         <v>41</v>
       </c>
       <c r="P611" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q611" s="2">
         <v>23628.3</v>
@@ -55110,7 +55110,7 @@
         <v>34</v>
       </c>
       <c r="P612" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q612" s="2">
         <v>19594.199999999997</v>
@@ -55172,7 +55172,7 @@
         <v>24</v>
       </c>
       <c r="P613" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q613" s="2">
         <v>13831.199999999999</v>
@@ -55234,7 +55234,7 @@
         <v>60</v>
       </c>
       <c r="P614" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q614" s="2">
         <v>34578</v>
@@ -55296,7 +55296,7 @@
         <v>46</v>
       </c>
       <c r="P615" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q615" s="2">
         <v>26861.699999999997</v>
@@ -55358,7 +55358,7 @@
         <v>34</v>
       </c>
       <c r="P616" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q616" s="2">
         <v>19854.3</v>
@@ -55420,7 +55420,7 @@
         <v>31</v>
       </c>
       <c r="P617" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q617" s="2">
         <v>18102.449999999997</v>
@@ -55482,7 +55482,7 @@
         <v>34</v>
       </c>
       <c r="P618" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q618" s="2">
         <v>19854.3</v>
@@ -55544,7 +55544,7 @@
         <v>36</v>
       </c>
       <c r="P619" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q619" s="2">
         <v>21022.199999999997</v>
@@ -55606,7 +55606,7 @@
         <v>24</v>
       </c>
       <c r="P620" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q620" s="2">
         <v>14014.8</v>
@@ -55668,7 +55668,7 @@
         <v>62</v>
       </c>
       <c r="P621" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q621" s="2">
         <v>36204.899999999994</v>
@@ -55730,7 +55730,7 @@
         <v>34</v>
       </c>
       <c r="P622" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q622" s="2">
         <v>19854.3</v>
@@ -55792,7 +55792,7 @@
         <v>25</v>
       </c>
       <c r="P623" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q623" s="2">
         <v>14598.749999999998</v>
@@ -55854,7 +55854,7 @@
         <v>32</v>
       </c>
       <c r="P624" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q624" s="2">
         <v>18686.399999999998</v>
@@ -55916,7 +55916,7 @@
         <v>46</v>
       </c>
       <c r="P625" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q625" s="2">
         <v>26861.699999999997</v>
@@ -55978,7 +55978,7 @@
         <v>39</v>
       </c>
       <c r="P626" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q626" s="2">
         <v>22774.05</v>
@@ -56040,7 +56040,7 @@
         <v>25</v>
       </c>
       <c r="P627" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q627" s="2">
         <v>14598.749999999998</v>
@@ -56102,7 +56102,7 @@
         <v>34</v>
       </c>
       <c r="P628" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q628" s="2">
         <v>19854.3</v>
@@ -56164,7 +56164,7 @@
         <v>40</v>
       </c>
       <c r="P629" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q629" s="2">
         <v>23358</v>
@@ -56226,7 +56226,7 @@
         <v>52</v>
       </c>
       <c r="P630" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q630" s="2">
         <v>30365.399999999998</v>
@@ -56288,7 +56288,7 @@
         <v>77</v>
       </c>
       <c r="P631" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q631" s="2">
         <v>44964.149999999994</v>
@@ -56350,7 +56350,7 @@
         <v>28</v>
       </c>
       <c r="P632" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q632" s="2">
         <v>16350.599999999999</v>
@@ -56412,7 +56412,7 @@
         <v>31</v>
       </c>
       <c r="P633" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q633" s="2">
         <v>18102.449999999997</v>
@@ -56474,7 +56474,7 @@
         <v>54</v>
       </c>
       <c r="P634" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q634" s="2">
         <v>31533.3</v>
@@ -56536,7 +56536,7 @@
         <v>24</v>
       </c>
       <c r="P635" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q635" s="2">
         <v>14014.8</v>
@@ -56598,7 +56598,7 @@
         <v>59</v>
       </c>
       <c r="P636" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q636" s="2">
         <v>34453.049999999996</v>
@@ -56660,7 +56660,7 @@
         <v>30</v>
       </c>
       <c r="P637" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q637" s="2">
         <v>17518.5</v>
@@ -56722,7 +56722,7 @@
         <v>48</v>
       </c>
       <c r="P638" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q638" s="2">
         <v>28029.599999999999</v>
@@ -56784,7 +56784,7 @@
         <v>32</v>
       </c>
       <c r="P639" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q639" s="2">
         <v>18686.399999999998</v>
@@ -56846,7 +56846,7 @@
         <v>34</v>
       </c>
       <c r="P640" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q640" s="2">
         <v>19854.3</v>
@@ -56908,7 +56908,7 @@
         <v>37</v>
       </c>
       <c r="P641" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q641" s="2">
         <v>21606.149999999998</v>
@@ -56970,7 +56970,7 @@
         <v>27</v>
       </c>
       <c r="P642" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q642" s="2">
         <v>15766.65</v>
@@ -57032,7 +57032,7 @@
         <v>34</v>
       </c>
       <c r="P643" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q643" s="2">
         <v>19854.3</v>
@@ -57094,7 +57094,7 @@
         <v>32</v>
       </c>
       <c r="P644" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q644" s="2">
         <v>18686.399999999998</v>
@@ -57156,7 +57156,7 @@
         <v>25</v>
       </c>
       <c r="P645" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q645" s="2">
         <v>14598.749999999998</v>
@@ -57218,7 +57218,7 @@
         <v>37</v>
       </c>
       <c r="P646" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q646" s="2">
         <v>21606.149999999998</v>
@@ -57280,7 +57280,7 @@
         <v>34</v>
       </c>
       <c r="P647" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q647" s="2">
         <v>19854.3</v>
@@ -57342,7 +57342,7 @@
         <v>47</v>
       </c>
       <c r="P648" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q648" s="2">
         <v>27445.649999999998</v>
@@ -57404,7 +57404,7 @@
         <v>24</v>
       </c>
       <c r="P649" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q649" s="2">
         <v>14014.8</v>
@@ -57466,7 +57466,7 @@
         <v>49</v>
       </c>
       <c r="P650" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q650" s="2">
         <v>28613.55</v>
@@ -57528,7 +57528,7 @@
         <v>26</v>
       </c>
       <c r="P651" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q651" s="2">
         <v>15182.699999999999</v>
@@ -57590,7 +57590,7 @@
         <v>31</v>
       </c>
       <c r="P652" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q652" s="2">
         <v>18102.449999999997</v>
@@ -57652,7 +57652,7 @@
         <v>32</v>
       </c>
       <c r="P653" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q653" s="2">
         <v>18686.399999999998</v>
@@ -57714,7 +57714,7 @@
         <v>41</v>
       </c>
       <c r="P654" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q654" s="2">
         <v>23941.949999999997</v>
@@ -57776,7 +57776,7 @@
         <v>33</v>
       </c>
       <c r="P655" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q655" s="2">
         <v>19186.199999999997</v>
@@ -57838,7 +57838,7 @@
         <v>75</v>
       </c>
       <c r="P656" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q656" s="2">
         <v>43605</v>
@@ -57900,7 +57900,7 @@
         <v>34</v>
       </c>
       <c r="P657" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q657" s="2">
         <v>19767.599999999999</v>
@@ -57962,7 +57962,7 @@
         <v>35</v>
       </c>
       <c r="P658" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q658" s="2">
         <v>20349</v>
@@ -58024,7 +58024,7 @@
         <v>25</v>
       </c>
       <c r="P659" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q659" s="2">
         <v>14534.999999999998</v>
@@ -58086,7 +58086,7 @@
         <v>60</v>
       </c>
       <c r="P660" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q660" s="2">
         <v>34884</v>
@@ -58148,7 +58148,7 @@
         <v>33</v>
       </c>
       <c r="P661" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q661" s="2">
         <v>19186.199999999997</v>
@@ -58210,7 +58210,7 @@
         <v>46</v>
       </c>
       <c r="P662" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q662" s="2">
         <v>26744.399999999998</v>
@@ -58272,7 +58272,7 @@
         <v>53</v>
       </c>
       <c r="P663" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q663" s="2">
         <v>30814.199999999997</v>
@@ -58334,7 +58334,7 @@
         <v>37</v>
       </c>
       <c r="P664" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q664" s="2">
         <v>21511.8</v>
@@ -58396,7 +58396,7 @@
         <v>37</v>
       </c>
       <c r="P665" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q665" s="2">
         <v>21511.8</v>
@@ -58458,7 +58458,7 @@
         <v>58</v>
       </c>
       <c r="P666" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q666" s="2">
         <v>33721.199999999997</v>
@@ -58520,7 +58520,7 @@
         <v>57</v>
       </c>
       <c r="P667" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q667" s="2">
         <v>33139.799999999996</v>
@@ -58582,7 +58582,7 @@
         <v>24</v>
       </c>
       <c r="P668" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q668" s="2">
         <v>13953.599999999999</v>
@@ -58644,7 +58644,7 @@
         <v>65</v>
       </c>
       <c r="P669" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q669" s="2">
         <v>37791</v>
@@ -58706,7 +58706,7 @@
         <v>35</v>
       </c>
       <c r="P670" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q670" s="2">
         <v>20349</v>
@@ -58768,7 +58768,7 @@
         <v>51</v>
       </c>
       <c r="P671" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q671" s="2">
         <v>29651.399999999998</v>
@@ -58830,7 +58830,7 @@
         <v>68</v>
       </c>
       <c r="P672" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q672" s="2">
         <v>39535.199999999997</v>
@@ -58892,7 +58892,7 @@
         <v>53</v>
       </c>
       <c r="P673" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q673" s="2">
         <v>30814.199999999997</v>
@@ -58954,7 +58954,7 @@
         <v>98</v>
       </c>
       <c r="P674" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q674" s="2">
         <v>56977.2</v>
@@ -59016,7 +59016,7 @@
         <v>28</v>
       </c>
       <c r="P675" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q675" s="2">
         <v>16279.199999999999</v>
@@ -59078,7 +59078,7 @@
         <v>66</v>
       </c>
       <c r="P676" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q676" s="2">
         <v>38372.399999999994</v>
@@ -59140,7 +59140,7 @@
         <v>28</v>
       </c>
       <c r="P677" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q677" s="2">
         <v>16279.199999999999</v>
@@ -59202,7 +59202,7 @@
         <v>35</v>
       </c>
       <c r="P678" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q678" s="2">
         <v>20349</v>
@@ -59264,7 +59264,7 @@
         <v>32</v>
       </c>
       <c r="P679" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q679" s="2">
         <v>18604.8</v>
@@ -59326,7 +59326,7 @@
         <v>50</v>
       </c>
       <c r="P680" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q680" s="2">
         <v>29069.999999999996</v>
@@ -59388,7 +59388,7 @@
         <v>42</v>
       </c>
       <c r="P681" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q681" s="2">
         <v>24418.799999999999</v>
@@ -59450,7 +59450,7 @@
         <v>34</v>
       </c>
       <c r="P682" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q682" s="2">
         <v>19767.599999999999</v>
@@ -59512,7 +59512,7 @@
         <v>34</v>
       </c>
       <c r="P683" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q683" s="2">
         <v>19767.599999999999</v>
@@ -59574,7 +59574,7 @@
         <v>51</v>
       </c>
       <c r="P684" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q684" s="2">
         <v>27570.6</v>
@@ -59636,7 +59636,7 @@
         <v>36</v>
       </c>
       <c r="P685" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q685" s="2">
         <v>19461.599999999999</v>
@@ -59698,7 +59698,7 @@
         <v>28</v>
       </c>
       <c r="P686" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q686" s="2">
         <v>15136.8</v>
@@ -59760,7 +59760,7 @@
         <v>37</v>
       </c>
       <c r="P687" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q687" s="2">
         <v>20002.199999999997</v>
@@ -59822,7 +59822,7 @@
         <v>34</v>
       </c>
       <c r="P688" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q688" s="2">
         <v>18380.399999999998</v>
@@ -59884,7 +59884,7 @@
         <v>46</v>
       </c>
       <c r="P689" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q689" s="2">
         <v>24867.599999999999</v>
@@ -59946,7 +59946,7 @@
         <v>46</v>
       </c>
       <c r="P690" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q690" s="2">
         <v>24867.599999999999</v>
@@ -60008,7 +60008,7 @@
         <v>116</v>
       </c>
       <c r="P691" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q691" s="2">
         <v>62709.599999999999</v>
@@ -60070,7 +60070,7 @@
         <v>41</v>
       </c>
       <c r="P692" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q692" s="2">
         <v>22164.6</v>
@@ -60132,7 +60132,7 @@
         <v>36</v>
       </c>
       <c r="P693" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q693" s="2">
         <v>19461.599999999999</v>
@@ -60194,7 +60194,7 @@
         <v>24</v>
       </c>
       <c r="P694" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q694" s="2">
         <v>12974.4</v>
@@ -60256,7 +60256,7 @@
         <v>37</v>
       </c>
       <c r="P695" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q695" s="2">
         <v>20002.199999999997</v>
@@ -60318,7 +60318,7 @@
         <v>52</v>
       </c>
       <c r="P696" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q696" s="2">
         <v>28111.199999999997</v>
@@ -60380,7 +60380,7 @@
         <v>25</v>
       </c>
       <c r="P697" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q697" s="2">
         <v>13514.999999999998</v>
@@ -60442,7 +60442,7 @@
         <v>27</v>
       </c>
       <c r="P698" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q698" s="2">
         <v>14596.199999999999</v>
@@ -60504,7 +60504,7 @@
         <v>32</v>
       </c>
       <c r="P699" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q699" s="2">
         <v>17299.199999999997</v>
@@ -60566,7 +60566,7 @@
         <v>49</v>
       </c>
       <c r="P700" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q700" s="2">
         <v>26489.399999999998</v>
@@ -60628,7 +60628,7 @@
         <v>40</v>
       </c>
       <c r="P701" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q701" s="2">
         <v>21624</v>
@@ -60690,7 +60690,7 @@
         <v>45</v>
       </c>
       <c r="P702" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q702" s="2">
         <v>24327</v>
@@ -60752,7 +60752,7 @@
         <v>27</v>
       </c>
       <c r="P703" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q703" s="2">
         <v>14596.199999999999</v>
@@ -60814,7 +60814,7 @@
         <v>30</v>
       </c>
       <c r="P704" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q704" s="2">
         <v>16217.999999999998</v>
@@ -60876,7 +60876,7 @@
         <v>42</v>
       </c>
       <c r="P705" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q705" s="2">
         <v>22705.199999999997</v>
@@ -60938,7 +60938,7 @@
         <v>139</v>
       </c>
       <c r="P706" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q706" s="2">
         <v>74080.049999999988</v>
@@ -61000,7 +61000,7 @@
         <v>44</v>
       </c>
       <c r="P707" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q707" s="2">
         <v>23449.8</v>
@@ -61062,7 +61062,7 @@
         <v>52</v>
       </c>
       <c r="P708" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q708" s="2">
         <v>27713.399999999998</v>
@@ -61124,7 +61124,7 @@
         <v>39</v>
       </c>
       <c r="P709" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q709" s="2">
         <v>20785.05</v>
@@ -61186,7 +61186,7 @@
         <v>37</v>
       </c>
       <c r="P710" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q710" s="2">
         <v>19719.149999999998</v>
@@ -61248,7 +61248,7 @@
         <v>47</v>
       </c>
       <c r="P711" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q711" s="2">
         <v>25048.649999999998</v>
@@ -61310,7 +61310,7 @@
         <v>40</v>
       </c>
       <c r="P712" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q712" s="2">
         <v>21318</v>
@@ -61372,7 +61372,7 @@
         <v>47</v>
       </c>
       <c r="P713" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q713" s="2">
         <v>25048.649999999998</v>
@@ -61434,7 +61434,7 @@
         <v>34</v>
       </c>
       <c r="P714" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q714" s="2">
         <v>18120.3</v>
@@ -61496,7 +61496,7 @@
         <v>35</v>
       </c>
       <c r="P715" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q715" s="2">
         <v>18653.25</v>
@@ -61558,7 +61558,7 @@
         <v>37</v>
       </c>
       <c r="P716" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q716" s="2">
         <v>19719.149999999998</v>
@@ -61620,7 +61620,7 @@
         <v>63</v>
       </c>
       <c r="P717" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q717" s="2">
         <v>33575.85</v>
@@ -61682,7 +61682,7 @@
         <v>62</v>
       </c>
       <c r="P718" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q718" s="2">
         <v>33042.899999999994</v>
@@ -61744,7 +61744,7 @@
         <v>28</v>
       </c>
       <c r="P719" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q719" s="2">
         <v>14922.599999999999</v>
@@ -61806,7 +61806,7 @@
         <v>36</v>
       </c>
       <c r="P720" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q720" s="2">
         <v>19186.199999999997</v>
@@ -61868,7 +61868,7 @@
         <v>25</v>
       </c>
       <c r="P721" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q721" s="2">
         <v>13323.749999999998</v>
@@ -61930,7 +61930,7 @@
         <v>34</v>
       </c>
       <c r="P722" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q722" s="2">
         <v>18120.3</v>
@@ -61992,7 +61992,7 @@
         <v>29</v>
       </c>
       <c r="P723" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q723" s="2">
         <v>15455.55</v>
@@ -62054,7 +62054,7 @@
         <v>30</v>
       </c>
       <c r="P724" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q724" s="2">
         <v>15988.499999999998</v>
@@ -62116,7 +62116,7 @@
         <v>68</v>
       </c>
       <c r="P725" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q725" s="2">
         <v>36240.6</v>
@@ -62178,7 +62178,7 @@
         <v>27</v>
       </c>
       <c r="P726" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q726" s="2">
         <v>14389.65</v>
@@ -62240,7 +62240,7 @@
         <v>36</v>
       </c>
       <c r="P727" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q727" s="2">
         <v>19186.199999999997</v>
@@ -62302,7 +62302,7 @@
         <v>24</v>
       </c>
       <c r="P728" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q728" s="2">
         <v>12790.8</v>
@@ -62364,7 +62364,7 @@
         <v>41</v>
       </c>
       <c r="P729" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q729" s="2">
         <v>21850.949999999997</v>
@@ -62426,7 +62426,7 @@
         <v>30</v>
       </c>
       <c r="P730" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q730" s="2">
         <v>15988.499999999998</v>
@@ -62488,7 +62488,7 @@
         <v>24</v>
       </c>
       <c r="P731" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q731" s="2">
         <v>12790.8</v>
@@ -62550,7 +62550,7 @@
         <v>46</v>
       </c>
       <c r="P732" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q732" s="2">
         <v>24515.699999999997</v>
@@ -62612,7 +62612,7 @@
         <v>31</v>
       </c>
       <c r="P733" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q733" s="2">
         <v>16521.449999999997</v>
@@ -62674,7 +62674,7 @@
         <v>45</v>
       </c>
       <c r="P734" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q734" s="2">
         <v>23982.75</v>
@@ -62736,7 +62736,7 @@
         <v>95</v>
       </c>
       <c r="P735" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q735" s="2">
         <v>50388</v>
@@ -62798,7 +62798,7 @@
         <v>39</v>
       </c>
       <c r="P736" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q736" s="2">
         <v>20685.599999999999</v>
@@ -62860,7 +62860,7 @@
         <v>37</v>
       </c>
       <c r="P737" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q737" s="2">
         <v>19624.8</v>
@@ -62922,7 +62922,7 @@
         <v>55</v>
       </c>
       <c r="P738" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q738" s="2">
         <v>33940.5</v>
@@ -62984,7 +62984,7 @@
         <v>24</v>
       </c>
       <c r="P739" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q739" s="2">
         <v>13831.199999999999</v>
@@ -63046,7 +63046,7 @@
         <v>58</v>
       </c>
       <c r="P740" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q740" s="2">
         <v>35643.899999999994</v>
@@ -63108,7 +63108,7 @@
         <v>67</v>
       </c>
       <c r="P741" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q741" s="2">
         <v>41345.699999999997</v>
@@ -63170,7 +63170,7 @@
         <v>54</v>
       </c>
       <c r="P742" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q742" s="2">
         <v>33323.399999999994</v>
@@ -63232,7 +63232,7 @@
         <v>49</v>
       </c>
       <c r="P743" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q743" s="2">
         <v>30112.949999999997</v>
@@ -63294,7 +63294,7 @@
         <v>74</v>
       </c>
       <c r="P744" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q744" s="2">
         <v>46986.299999999996</v>
@@ -63356,7 +63356,7 @@
         <v>50</v>
       </c>
       <c r="P745" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q745" s="2">
         <v>30727.499999999996</v>
@@ -63418,7 +63418,7 @@
         <v>57</v>
       </c>
       <c r="P746" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q746" s="2">
         <v>36192.149999999994</v>
@@ -63478,7 +63478,7 @@
         <v>0</v>
       </c>
       <c r="P747" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q747" s="2">
         <v>0</v>
@@ -63535,7 +63535,7 @@
         <v>0</v>
       </c>
       <c r="P748" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q748" s="2">
         <v>0</v>
@@ -63594,7 +63594,7 @@
         <v>47</v>
       </c>
       <c r="P749" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q749" s="2">
         <v>29842.649999999998</v>
@@ -63656,7 +63656,7 @@
         <v>46</v>
       </c>
       <c r="P750" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q750" s="2">
         <v>28269.3</v>
@@ -63718,7 +63718,7 @@
         <v>56</v>
       </c>
       <c r="P751" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q751" s="2">
         <v>35557.199999999997</v>
@@ -63780,7 +63780,7 @@
         <v>52</v>
       </c>
       <c r="P752" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q752" s="2">
         <v>31956.6</v>
@@ -63842,7 +63842,7 @@
         <v>40</v>
       </c>
       <c r="P753" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q753" s="2">
         <v>24582</v>
@@ -63904,7 +63904,7 @@
         <v>39</v>
       </c>
       <c r="P754" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q754" s="2">
         <v>23967.449999999997</v>
@@ -63966,7 +63966,7 @@
         <v>40</v>
       </c>
       <c r="P755" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q755" s="2">
         <v>25398</v>
@@ -64028,7 +64028,7 @@
         <v>39</v>
       </c>
       <c r="P756" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q756" s="2">
         <v>24066.899999999998</v>
@@ -64088,7 +64088,7 @@
         <v>0</v>
       </c>
       <c r="P757" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q757" s="2">
         <v>0</v>
@@ -64147,7 +64147,7 @@
         <v>43</v>
       </c>
       <c r="P758" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q758" s="2">
         <v>26535.3</v>
@@ -64209,7 +64209,7 @@
         <v>43</v>
       </c>
       <c r="P759" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q759" s="2">
         <v>26535.3</v>
@@ -64271,7 +64271,7 @@
         <v>31</v>
       </c>
       <c r="P760" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q760" s="2">
         <v>18972</v>
@@ -64333,7 +64333,7 @@
         <v>49</v>
       </c>
       <c r="P761" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q761" s="2">
         <v>30237.899999999998</v>
@@ -64395,7 +64395,7 @@
         <v>49</v>
       </c>
       <c r="P762" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q762" s="2">
         <v>30112.949999999997</v>
@@ -64457,7 +64457,7 @@
         <v>40</v>
       </c>
       <c r="P763" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q763" s="2">
         <v>24684</v>
@@ -64519,7 +64519,7 @@
         <v>35</v>
       </c>
       <c r="P764" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q764" s="2">
         <v>21509.25</v>
@@ -64581,7 +64581,7 @@
         <v>26</v>
       </c>
       <c r="P765" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q765" s="2">
         <v>15978.3</v>
@@ -64643,7 +64643,7 @@
         <v>203</v>
       </c>
       <c r="P766" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q766" s="2">
         <v>125271.29999999999</v>
@@ -64705,7 +64705,7 @@
         <v>36</v>
       </c>
       <c r="P767" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q767" s="2">
         <v>22123.8</v>
@@ -64767,7 +64767,7 @@
         <v>34</v>
       </c>
       <c r="P768" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q768" s="2">
         <v>17253.3</v>
@@ -64829,7 +64829,7 @@
         <v>34</v>
       </c>
       <c r="P769" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q769" s="2">
         <v>20981.399999999998</v>
@@ -64891,7 +64891,7 @@
         <v>56</v>
       </c>
       <c r="P770" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q770" s="2">
         <v>34414.799999999996</v>
@@ -64953,7 +64953,7 @@
         <v>37</v>
       </c>
       <c r="P771" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q771" s="2">
         <v>22738.35</v>
@@ -65015,7 +65015,7 @@
         <v>36</v>
       </c>
       <c r="P772" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q772" s="2">
         <v>10740.599999999999</v>
@@ -65077,7 +65077,7 @@
         <v>42</v>
       </c>
       <c r="P773" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q773" s="2">
         <v>25918.199999999997</v>
@@ -65139,7 +65139,7 @@
         <v>34</v>
       </c>
       <c r="P774" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q774" s="2">
         <v>17946.899999999998</v>
@@ -65201,7 +65201,7 @@
         <v>36</v>
       </c>
       <c r="P775" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q775" s="2">
         <v>19002.599999999999</v>
@@ -65263,7 +65263,7 @@
         <v>39</v>
       </c>
       <c r="P776" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q776" s="2">
         <v>24066.899999999998</v>
@@ -65325,7 +65325,7 @@
         <v>40</v>
       </c>
       <c r="P777" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q777" s="2">
         <v>24582</v>
@@ -65385,7 +65385,7 @@
         <v>0</v>
       </c>
       <c r="P778" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q778" s="2">
         <v>0</v>
@@ -65444,7 +65444,7 @@
         <v>33</v>
       </c>
       <c r="P779" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q779" s="2">
         <v>20953.349999999999</v>
@@ -65506,7 +65506,7 @@
         <v>32</v>
       </c>
       <c r="P780" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q780" s="2">
         <v>19747.199999999997</v>
@@ -65568,7 +65568,7 @@
         <v>39</v>
       </c>
       <c r="P781" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q781" s="2">
         <v>23967.449999999997</v>
@@ -65630,7 +65630,7 @@
         <v>37</v>
       </c>
       <c r="P782" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q782" s="2">
         <v>22738.35</v>
@@ -65692,7 +65692,7 @@
         <v>33</v>
       </c>
       <c r="P783" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q783" s="2">
         <v>20280.149999999998</v>
@@ -65754,7 +65754,7 @@
         <v>39</v>
       </c>
       <c r="P784" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q784" s="2">
         <v>24066.899999999998</v>
@@ -65816,7 +65816,7 @@
         <v>26</v>
       </c>
       <c r="P785" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q785" s="2">
         <v>16508.699999999997</v>
@@ -65878,7 +65878,7 @@
         <v>34</v>
       </c>
       <c r="P786" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q786" s="2">
         <v>19680.899999999998</v>
@@ -65940,7 +65940,7 @@
         <v>26</v>
       </c>
       <c r="P787" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q787" s="2">
         <v>7757.0999999999995</v>
@@ -66002,7 +66002,7 @@
         <v>34</v>
       </c>
       <c r="P788" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q788" s="2">
         <v>20981.399999999998</v>
@@ -66064,7 +66064,7 @@
         <v>42</v>
       </c>
       <c r="P789" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q789" s="2">
         <v>26667.899999999998</v>
@@ -66126,7 +66126,7 @@
         <v>34</v>
       </c>
       <c r="P790" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q790" s="2">
         <v>10143.9</v>
@@ -66188,7 +66188,7 @@
         <v>45</v>
       </c>
       <c r="P791" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q791" s="2">
         <v>27769.499999999996</v>
@@ -66250,7 +66250,7 @@
         <v>34</v>
       </c>
       <c r="P792" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q792" s="2">
         <v>21588.3</v>
@@ -66312,7 +66312,7 @@
         <v>38</v>
       </c>
       <c r="P793" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q793" s="2">
         <v>19283.099999999999</v>
@@ -66374,7 +66374,7 @@
         <v>30</v>
       </c>
       <c r="P794" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q794" s="2">
         <v>18436.5</v>
@@ -66436,7 +66436,7 @@
         <v>43</v>
       </c>
       <c r="P795" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q795" s="2">
         <v>26535.3</v>
@@ -66498,7 +66498,7 @@
         <v>34</v>
       </c>
       <c r="P796" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q796" s="2">
         <v>20981.399999999998</v>
@@ -66560,7 +66560,7 @@
         <v>30</v>
       </c>
       <c r="P797" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q797" s="2">
         <v>18436.5</v>
@@ -66622,7 +66622,7 @@
         <v>29</v>
       </c>
       <c r="P798" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q798" s="2">
         <v>17821.949999999997</v>
@@ -66684,7 +66684,7 @@
         <v>37</v>
       </c>
       <c r="P799" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q799" s="2">
         <v>22832.699999999997</v>
@@ -66746,7 +66746,7 @@
         <v>55</v>
       </c>
       <c r="P800" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q800" s="2">
         <v>32117.249999999996</v>
@@ -66808,7 +66808,7 @@
         <v>27</v>
       </c>
       <c r="P801" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q801" s="2">
         <v>16592.849999999999</v>
@@ -66870,7 +66870,7 @@
         <v>44</v>
       </c>
       <c r="P802" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q802" s="2">
         <v>27040.199999999997</v>
@@ -66932,7 +66932,7 @@
         <v>45</v>
       </c>
       <c r="P803" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q803" s="2">
         <v>27654.749999999996</v>
@@ -66994,7 +66994,7 @@
         <v>24</v>
       </c>
       <c r="P804" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q804" s="2">
         <v>14810.4</v>
@@ -67056,7 +67056,7 @@
         <v>24</v>
       </c>
       <c r="P805" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q805" s="2">
         <v>14749.199999999999</v>
@@ -67118,7 +67118,7 @@
         <v>24</v>
       </c>
       <c r="P806" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q806" s="2">
         <v>14749.199999999999</v>
@@ -67180,7 +67180,7 @@
         <v>34</v>
       </c>
       <c r="P807" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q807" s="2">
         <v>20981.399999999998</v>
@@ -67242,7 +67242,7 @@
         <v>26</v>
       </c>
       <c r="P808" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q808" s="2">
         <v>16044.599999999999</v>
@@ -67304,7 +67304,7 @@
         <v>26</v>
       </c>
       <c r="P809" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q809" s="2">
         <v>16044.599999999999</v>
@@ -67366,7 +67366,7 @@
         <v>24</v>
       </c>
       <c r="P810" s="2">
-        <v>3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q810" s="2">
         <v>14810.4</v>
